--- a/结果/问题三_运输调度_修复版.xlsx
+++ b/结果/问题三_运输调度_修复版.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
   <si>
     <t>mission_id</t>
   </si>
@@ -58,6 +58,18 @@
     <t>charge_min</t>
   </si>
   <si>
+    <t>cargo_count</t>
+  </si>
+  <si>
+    <t>original_start_min</t>
+  </si>
+  <si>
+    <t>original_delivery_min</t>
+  </si>
+  <si>
+    <t>original_end_min</t>
+  </si>
+  <si>
     <t>communication_mode</t>
   </si>
   <si>
@@ -67,18 +79,18 @@
     <t>UC01</t>
   </si>
   <si>
+    <t>UB01</t>
+  </si>
+  <si>
+    <t>UA01</t>
+  </si>
+  <si>
+    <t>UB02</t>
+  </si>
+  <si>
     <t>UC02</t>
   </si>
   <si>
-    <t>UA01</t>
-  </si>
-  <si>
-    <t>UB01</t>
-  </si>
-  <si>
-    <t>UB02</t>
-  </si>
-  <si>
     <t>UA02</t>
   </si>
   <si>
@@ -91,36 +103,39 @@
     <t>C</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>C-BAT-01</t>
   </si>
   <si>
+    <t>B-BAT-01</t>
+  </si>
+  <si>
+    <t>A-BAT-01</t>
+  </si>
+  <si>
+    <t>B-BAT-02</t>
+  </si>
+  <si>
+    <t>B-BAT-03</t>
+  </si>
+  <si>
+    <t>B-BAT-04</t>
+  </si>
+  <si>
     <t>C-BAT-02</t>
   </si>
   <si>
-    <t>A-BAT-01</t>
-  </si>
-  <si>
-    <t>B-BAT-01</t>
-  </si>
-  <si>
-    <t>B-BAT-02</t>
-  </si>
-  <si>
-    <t>B-BAT-03</t>
+    <t>A-BAT-02</t>
   </si>
   <si>
     <t>C-BAT-03</t>
   </si>
   <si>
-    <t>A-BAT-02</t>
-  </si>
-  <si>
     <t>C-BAT-04</t>
   </si>
   <si>
@@ -136,9 +151,6 @@
     <t>A-BAT-06</t>
   </si>
   <si>
-    <t>B-BAT-04</t>
-  </si>
-  <si>
     <t>S001</t>
   </si>
   <si>
@@ -331,10 +343,7 @@
     <t>S005-HYG-01</t>
   </si>
   <si>
-    <t>relay_outside_service_window</t>
-  </si>
-  <si>
-    <t>interrupted</t>
+    <t>direct</t>
   </si>
   <si>
     <t>R02</t>
@@ -698,10 +707,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:T50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -750,25 +759,37 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -794,40 +815,52 @@
       <c r="N2">
         <v>25.43953939025919</v>
       </c>
-      <c r="O2" t="s">
-        <v>105</v>
-      </c>
-      <c r="P2" t="b">
+      <c r="O2">
+        <v>7</v>
+      </c>
+      <c r="P2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2">
+        <v>20.89825141136788</v>
+      </c>
+      <c r="R2">
+        <v>26.19033615606908</v>
+      </c>
+      <c r="S2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>16.49825141136787</v>
+        <v>15.37289355636781</v>
       </c>
       <c r="I3">
-        <v>21.79033615606908</v>
+        <v>20.30834266829118</v>
       </c>
       <c r="J3">
         <v>60</v>
@@ -836,48 +869,60 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2.066398756230736</v>
+        <v>1.063798065282268</v>
       </c>
       <c r="M3">
-        <v>0.741700155471158</v>
+        <v>0.734050483679433</v>
       </c>
       <c r="N3">
-        <v>23.21638327465262</v>
-      </c>
-      <c r="O3" t="s">
-        <v>105</v>
-      </c>
-      <c r="P3" t="b">
+        <v>18.79409713814971</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3">
+        <v>15.37289355636781</v>
+      </c>
+      <c r="R3">
+        <v>20.30834266829118</v>
+      </c>
+      <c r="S3" t="s">
+        <v>109</v>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H4">
-        <v>21.41832151107866</v>
+        <v>31.32399636262702</v>
       </c>
       <c r="I4">
-        <v>33.43864302215731</v>
+        <v>43.34431787370568</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -894,31 +939,43 @@
       <c r="N4">
         <v>19.9917309426066</v>
       </c>
-      <c r="O4" t="s">
-        <v>106</v>
-      </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="O4">
+        <v>2</v>
+      </c>
+      <c r="P4">
+        <v>9.905674851548365</v>
+      </c>
+      <c r="Q4">
+        <v>31.32399636262702</v>
+      </c>
+      <c r="R4">
+        <v>43.34431787370568</v>
+      </c>
+      <c r="S4" t="s">
+        <v>110</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -944,40 +1001,52 @@
       <c r="N5">
         <v>18.96225489436069</v>
       </c>
-      <c r="O5" t="s">
-        <v>106</v>
-      </c>
-      <c r="P5" t="b">
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5">
+        <v>14.67766295665795</v>
+      </c>
+      <c r="R5">
+        <v>20.06321480220478</v>
+      </c>
+      <c r="S5" t="s">
+        <v>109</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="H6">
-        <v>14.67766295665795</v>
+        <v>34.74087775886273</v>
       </c>
       <c r="I6">
-        <v>20.06321480220478</v>
+        <v>40.12642960440956</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -994,40 +1063,52 @@
       <c r="N6">
         <v>18.05402461630594</v>
       </c>
-      <c r="O6" t="s">
-        <v>106</v>
-      </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6">
+        <v>20.06321480220478</v>
+      </c>
+      <c r="Q6">
+        <v>34.74087775886273</v>
+      </c>
+      <c r="R6">
+        <v>40.12642960440956</v>
+      </c>
+      <c r="S6" t="s">
+        <v>109</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>20.06321480220478</v>
+        <v>20.30834266829118</v>
       </c>
       <c r="H7">
-        <v>37.73344021144993</v>
+        <v>37.97856807753634</v>
       </c>
       <c r="I7">
-        <v>46.14899895402841</v>
+        <v>46.39412682011481</v>
       </c>
       <c r="J7">
         <v>60</v>
@@ -1044,40 +1125,52 @@
       <c r="N7">
         <v>22.67315925210164</v>
       </c>
-      <c r="O7" t="s">
-        <v>106</v>
-      </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7">
+        <v>20.30834266829118</v>
+      </c>
+      <c r="Q7">
+        <v>37.97856807753634</v>
+      </c>
+      <c r="R7">
+        <v>46.39412682011481</v>
+      </c>
+      <c r="S7" t="s">
+        <v>111</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>21.79033615606908</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H8">
-        <v>39.97576375627399</v>
+        <v>28.09110245175328</v>
       </c>
       <c r="I8">
-        <v>48.33435802314556</v>
+        <v>36.44969671862485</v>
       </c>
       <c r="J8">
         <v>60</v>
@@ -1094,40 +1187,52 @@
       <c r="N8">
         <v>27.0257293895793</v>
       </c>
-      <c r="O8" t="s">
-        <v>106</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="O8">
+        <v>2</v>
+      </c>
+      <c r="P8">
+        <v>9.905674851548365</v>
+      </c>
+      <c r="Q8">
+        <v>28.09110245175328</v>
+      </c>
+      <c r="R8">
+        <v>36.44969671862485</v>
+      </c>
+      <c r="S8" t="s">
+        <v>110</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H9">
-        <v>18.04073685958943</v>
+        <v>27.9464117111378</v>
       </c>
       <c r="I9">
-        <v>26.83036260806776</v>
+        <v>36.73603745961613</v>
       </c>
       <c r="J9">
         <v>60</v>
@@ -1144,31 +1249,43 @@
       <c r="N9">
         <v>16.21694297621002</v>
       </c>
-      <c r="O9" t="s">
-        <v>106</v>
-      </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <v>9.905674851548365</v>
+      </c>
+      <c r="Q9">
+        <v>27.9464117111378</v>
+      </c>
+      <c r="R9">
+        <v>36.73603745961613</v>
+      </c>
+      <c r="S9" t="s">
+        <v>110</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>26.19033615606908</v>
@@ -1194,40 +1311,52 @@
       <c r="N10">
         <v>33.39289855274107</v>
       </c>
-      <c r="O10" t="s">
-        <v>106</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="O10">
+        <v>2</v>
+      </c>
+      <c r="P10">
+        <v>26.19033615606908</v>
+      </c>
+      <c r="Q10">
+        <v>47.61045803875672</v>
+      </c>
+      <c r="R10">
+        <v>59.08407992144435</v>
+      </c>
+      <c r="S10" t="s">
+        <v>110</v>
+      </c>
+      <c r="T10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>36.44969671862485</v>
       </c>
       <c r="H11">
-        <v>21.21667202957535</v>
+        <v>57.78439582356296</v>
       </c>
       <c r="I11">
-        <v>33.18145517026183</v>
+        <v>69.29126159516773</v>
       </c>
       <c r="J11">
         <v>60</v>
@@ -1236,48 +1365,60 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>1.974536954059142</v>
+        <v>3.58861224407448</v>
       </c>
       <c r="M11">
-        <v>0.5612140102090795</v>
+        <v>0.55142346949069</v>
       </c>
       <c r="N11">
-        <v>17.84036311213661</v>
-      </c>
-      <c r="O11" t="s">
-        <v>106</v>
-      </c>
-      <c r="P11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>30.0874858239473</v>
+      </c>
+      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="P11">
+        <v>9.905674851548365</v>
+      </c>
+      <c r="Q11">
+        <v>31.24037395648647</v>
+      </c>
+      <c r="R11">
+        <v>42.74723972809124</v>
+      </c>
+      <c r="S11" t="s">
+        <v>110</v>
+      </c>
+      <c r="T11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H12">
-        <v>20.41832151107866</v>
+        <v>30.32399636262702</v>
       </c>
       <c r="I12">
-        <v>32.43864302215731</v>
+        <v>42.34431787370568</v>
       </c>
       <c r="J12">
         <v>60</v>
@@ -1294,40 +1435,52 @@
       <c r="N12">
         <v>19.83047220515579</v>
       </c>
-      <c r="O12" t="s">
-        <v>106</v>
-      </c>
-      <c r="P12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>9.905674851548365</v>
+      </c>
+      <c r="Q12">
+        <v>30.32399636262702</v>
+      </c>
+      <c r="R12">
+        <v>42.34431787370568</v>
+      </c>
+      <c r="S12" t="s">
+        <v>110</v>
+      </c>
+      <c r="T12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G13">
-        <v>26.83036260806776</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H13">
-        <v>47.24868411914642</v>
+        <v>30.32399636262702</v>
       </c>
       <c r="I13">
-        <v>59.26900563022507</v>
+        <v>42.34431787370568</v>
       </c>
       <c r="J13">
         <v>60</v>
@@ -1344,40 +1497,52 @@
       <c r="N13">
         <v>19.83047220515579</v>
       </c>
-      <c r="O13" t="s">
-        <v>106</v>
-      </c>
-      <c r="P13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>36.73603745961613</v>
+      </c>
+      <c r="Q13">
+        <v>57.15435897069479</v>
+      </c>
+      <c r="R13">
+        <v>69.17468048177344</v>
+      </c>
+      <c r="S13" t="s">
+        <v>110</v>
+      </c>
+      <c r="T13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G14">
-        <v>32.43864302215731</v>
+        <v>36.73603745961613</v>
       </c>
       <c r="H14">
-        <v>52.85696453323597</v>
+        <v>57.15435897069479</v>
       </c>
       <c r="I14">
-        <v>64.87728604431462</v>
+        <v>69.17468048177344</v>
       </c>
       <c r="J14">
         <v>60</v>
@@ -1394,40 +1559,52 @@
       <c r="N14">
         <v>19.83047220515579</v>
       </c>
-      <c r="O14" t="s">
-        <v>106</v>
-      </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>42.34431787370568</v>
+      </c>
+      <c r="Q14">
+        <v>62.76263938478434</v>
+      </c>
+      <c r="R14">
+        <v>74.78296089586298</v>
+      </c>
+      <c r="S14" t="s">
+        <v>110</v>
+      </c>
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G15">
-        <v>20.06321480220478</v>
+        <v>40.12642960440956</v>
       </c>
       <c r="H15">
-        <v>36.73344021144993</v>
+        <v>56.79665501365471</v>
       </c>
       <c r="I15">
-        <v>45.14899895402841</v>
+        <v>65.21221375623318</v>
       </c>
       <c r="J15">
         <v>60</v>
@@ -1444,40 +1621,52 @@
       <c r="N15">
         <v>20.34591921171301</v>
       </c>
-      <c r="O15" t="s">
-        <v>106</v>
-      </c>
-      <c r="P15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>40.12642960440956</v>
+      </c>
+      <c r="Q15">
+        <v>56.79665501365471</v>
+      </c>
+      <c r="R15">
+        <v>65.21221375623318</v>
+      </c>
+      <c r="S15" t="s">
+        <v>111</v>
+      </c>
+      <c r="T15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G16">
-        <v>48.33435802314556</v>
+        <v>59.08407992144435</v>
       </c>
       <c r="H16">
-        <v>74.58261198294738</v>
+        <v>85.33233388124617</v>
       </c>
       <c r="I16">
-        <v>87.68219927608253</v>
+        <v>98.4319211743813</v>
       </c>
       <c r="J16">
         <v>120</v>
@@ -1494,40 +1683,52 @@
       <c r="N16">
         <v>38.44670504800009</v>
       </c>
-      <c r="O16" t="s">
-        <v>106</v>
-      </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="O16">
+        <v>5</v>
+      </c>
+      <c r="P16">
+        <v>36.44969671862485</v>
+      </c>
+      <c r="Q16">
+        <v>62.69795067842667</v>
+      </c>
+      <c r="R16">
+        <v>75.79753797156181</v>
+      </c>
+      <c r="S16" t="s">
+        <v>111</v>
+      </c>
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G17">
-        <v>59.08407992144435</v>
+        <v>69.29126159516773</v>
       </c>
       <c r="H17">
-        <v>75.58233133281222</v>
+        <v>85.7895130065356</v>
       </c>
       <c r="I17">
-        <v>80.87441607751343</v>
+        <v>91.08159775123681</v>
       </c>
       <c r="J17">
         <v>120</v>
@@ -1544,40 +1745,52 @@
       <c r="N17">
         <v>22.53072017693587</v>
       </c>
-      <c r="O17" t="s">
-        <v>107</v>
-      </c>
-      <c r="P17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="O17">
+        <v>3</v>
+      </c>
+      <c r="P17">
+        <v>59.08407992144435</v>
+      </c>
+      <c r="Q17">
+        <v>75.58233133281222</v>
+      </c>
+      <c r="R17">
+        <v>80.87441607751343</v>
+      </c>
+      <c r="S17" t="s">
+        <v>109</v>
+      </c>
+      <c r="T17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G18">
-        <v>45.14899895402841</v>
+        <v>46.39412682011481</v>
       </c>
       <c r="H18">
-        <v>65.96660557946939</v>
+        <v>67.21173344555578</v>
       </c>
       <c r="I18">
-        <v>77.39598998268814</v>
+        <v>78.64111784877454</v>
       </c>
       <c r="J18">
         <v>120</v>
@@ -1594,40 +1807,52 @@
       <c r="N18">
         <v>29.50525516252995</v>
       </c>
-      <c r="O18" t="s">
-        <v>106</v>
-      </c>
-      <c r="P18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="O18">
+        <v>2</v>
+      </c>
+      <c r="P18">
+        <v>46.39412682011481</v>
+      </c>
+      <c r="Q18">
+        <v>67.21173344555578</v>
+      </c>
+      <c r="R18">
+        <v>78.64111784877454</v>
+      </c>
+      <c r="S18" t="s">
+        <v>110</v>
+      </c>
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G19">
-        <v>46.14899895402841</v>
+        <v>65.21221375623318</v>
       </c>
       <c r="H19">
-        <v>66.96660557946939</v>
+        <v>86.02982038167417</v>
       </c>
       <c r="I19">
-        <v>78.39598998268814</v>
+        <v>97.4592047848929</v>
       </c>
       <c r="J19">
         <v>120</v>
@@ -1644,40 +1869,52 @@
       <c r="N19">
         <v>27.29375830875431</v>
       </c>
-      <c r="O19" t="s">
-        <v>106</v>
-      </c>
-      <c r="P19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="O19">
+        <v>2</v>
+      </c>
+      <c r="P19">
+        <v>65.21221375623318</v>
+      </c>
+      <c r="Q19">
+        <v>86.02982038167417</v>
+      </c>
+      <c r="R19">
+        <v>97.4592047848929</v>
+      </c>
+      <c r="S19" t="s">
+        <v>110</v>
+      </c>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G20">
-        <v>43.04730558427778</v>
+        <v>42.34431787370568</v>
       </c>
       <c r="H20">
-        <v>65.80996203665651</v>
+        <v>65.10697432608441</v>
       </c>
       <c r="I20">
-        <v>79.23172960014637</v>
+        <v>78.52874188957426</v>
       </c>
       <c r="J20">
         <v>120</v>
@@ -1694,40 +1931,52 @@
       <c r="N20">
         <v>21.14282094321784</v>
       </c>
-      <c r="O20" t="s">
-        <v>106</v>
-      </c>
-      <c r="P20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="O20">
+        <v>2</v>
+      </c>
+      <c r="P20">
+        <v>52.95298043582615</v>
+      </c>
+      <c r="Q20">
+        <v>75.71563688820488</v>
+      </c>
+      <c r="R20">
+        <v>89.13740445169474</v>
+      </c>
+      <c r="S20" t="s">
+        <v>111</v>
+      </c>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G21">
-        <v>51.02181828239844</v>
+        <v>52.95298043582615</v>
       </c>
       <c r="H21">
-        <v>72.4401397934771</v>
+        <v>74.37130194690481</v>
       </c>
       <c r="I21">
-        <v>84.46046130455575</v>
+        <v>86.39162345798346</v>
       </c>
       <c r="J21">
         <v>120</v>
@@ -1744,40 +1993,52 @@
       <c r="N21">
         <v>19.93699173815082</v>
       </c>
-      <c r="O21" t="s">
-        <v>106</v>
-      </c>
-      <c r="P21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="O21">
+        <v>2</v>
+      </c>
+      <c r="P21">
+        <v>60.92749313394681</v>
+      </c>
+      <c r="Q21">
+        <v>82.34581464502547</v>
+      </c>
+      <c r="R21">
+        <v>94.36613615610412</v>
+      </c>
+      <c r="S21" t="s">
+        <v>110</v>
+      </c>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G22">
-        <v>59.26900563022507</v>
+        <v>62.17479007886146</v>
       </c>
       <c r="H22">
-        <v>81.0316620826038</v>
+        <v>83.9374465312402</v>
       </c>
       <c r="I22">
-        <v>94.45342964609364</v>
+        <v>97.35921409473004</v>
       </c>
       <c r="J22">
         <v>120</v>
@@ -1794,40 +2055,52 @@
       <c r="N22">
         <v>20.96694005268129</v>
       </c>
-      <c r="O22" t="s">
-        <v>106</v>
-      </c>
-      <c r="P22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>69.17468048177344</v>
+      </c>
+      <c r="Q22">
+        <v>90.93733693415217</v>
+      </c>
+      <c r="R22">
+        <v>104.359104497642</v>
+      </c>
+      <c r="S22" t="s">
+        <v>111</v>
+      </c>
+      <c r="T22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G23">
-        <v>80.87441607751343</v>
+        <v>92.47697847418542</v>
       </c>
       <c r="H23">
-        <v>100.3891190524401</v>
+        <v>111.9916814491121</v>
       </c>
       <c r="I23">
-        <v>111.3818220273667</v>
+        <v>122.9843844240387</v>
       </c>
       <c r="J23">
         <v>120</v>
@@ -1844,40 +2117,52 @@
       <c r="N23">
         <v>29.97262327978342</v>
       </c>
-      <c r="O23" t="s">
-        <v>106</v>
-      </c>
-      <c r="P23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>75.79753797156181</v>
+      </c>
+      <c r="Q23">
+        <v>95.31224094648847</v>
+      </c>
+      <c r="R23">
+        <v>106.3049439214151</v>
+      </c>
+      <c r="S23" t="s">
+        <v>111</v>
+      </c>
+      <c r="T23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G24">
-        <v>64.87728604431462</v>
+        <v>69.17468048177344</v>
       </c>
       <c r="H24">
-        <v>79.43856814387024</v>
+        <v>83.73596258132906</v>
       </c>
       <c r="I24">
-        <v>85.70773913231474</v>
+        <v>90.00513356977356</v>
       </c>
       <c r="J24">
         <v>120</v>
@@ -1894,40 +2179,52 @@
       <c r="N24">
         <v>13.46603783864191</v>
       </c>
-      <c r="O24" t="s">
-        <v>106</v>
-      </c>
-      <c r="P24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>74.78296089586298</v>
+      </c>
+      <c r="Q24">
+        <v>89.34424299541861</v>
+      </c>
+      <c r="R24">
+        <v>95.61341398386311</v>
+      </c>
+      <c r="S24" t="s">
+        <v>109</v>
+      </c>
+      <c r="T24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G25">
-        <v>79.23172960014637</v>
+        <v>78.52874188957426</v>
       </c>
       <c r="H25">
-        <v>97.16134990817106</v>
+        <v>96.45836219759896</v>
       </c>
       <c r="I25">
-        <v>106.8363035495291</v>
+        <v>106.133315838957</v>
       </c>
       <c r="J25">
         <v>120</v>
@@ -1944,40 +2241,52 @@
       <c r="N25">
         <v>15.89883979115685</v>
       </c>
-      <c r="O25" t="s">
-        <v>106</v>
-      </c>
-      <c r="P25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>89.13740445169474</v>
+      </c>
+      <c r="Q25">
+        <v>107.0670247597194</v>
+      </c>
+      <c r="R25">
+        <v>116.7419784010775</v>
+      </c>
+      <c r="S25" t="s">
+        <v>111</v>
+      </c>
+      <c r="T25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G26">
-        <v>84.7077582494704</v>
+        <v>89.00515268692922</v>
       </c>
       <c r="H26">
-        <v>102.0526042484469</v>
+        <v>106.3499986859057</v>
       </c>
       <c r="I26">
-        <v>111.1462280252011</v>
+        <v>115.4436224626599</v>
       </c>
       <c r="J26">
         <v>120</v>
@@ -1994,40 +2303,52 @@
       <c r="N26">
         <v>15.94811007851097</v>
       </c>
-      <c r="O26" t="s">
-        <v>106</v>
-      </c>
-      <c r="P26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>94.61343310101877</v>
+      </c>
+      <c r="Q26">
+        <v>111.9582790999953</v>
+      </c>
+      <c r="R26">
+        <v>121.0519028767495</v>
+      </c>
+      <c r="S26" t="s">
+        <v>110</v>
+      </c>
+      <c r="T26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E27" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G27">
-        <v>77.39598998268814</v>
+        <v>78.64111784877454</v>
       </c>
       <c r="H27">
-        <v>96.57940191634469</v>
+        <v>97.8245297824311</v>
       </c>
       <c r="I27">
-        <v>107.4318138500012</v>
+        <v>108.6769417160876</v>
       </c>
       <c r="J27">
         <v>120</v>
@@ -2044,40 +2365,52 @@
       <c r="N27">
         <v>25.35100588482284</v>
       </c>
-      <c r="O27" t="s">
-        <v>106</v>
-      </c>
-      <c r="P27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>78.64111784877454</v>
+      </c>
+      <c r="Q27">
+        <v>97.8245297824311</v>
+      </c>
+      <c r="R27">
+        <v>108.6769417160876</v>
+      </c>
+      <c r="S27" t="s">
+        <v>110</v>
+      </c>
+      <c r="T27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F28" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G28">
-        <v>78.39598998268814</v>
+        <v>97.4592047848929</v>
       </c>
       <c r="H28">
-        <v>94.08986564711097</v>
+        <v>113.1530804493157</v>
       </c>
       <c r="I28">
-        <v>101.5326302004227</v>
+        <v>120.5958450026275</v>
       </c>
       <c r="J28">
         <v>120</v>
@@ -2094,40 +2427,52 @@
       <c r="N28">
         <v>20.57057180524388</v>
       </c>
-      <c r="O28" t="s">
-        <v>106</v>
-      </c>
-      <c r="P28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28">
+        <v>97.4592047848929</v>
+      </c>
+      <c r="Q28">
+        <v>113.1530804493157</v>
+      </c>
+      <c r="R28">
+        <v>120.5958450026275</v>
+      </c>
+      <c r="S28" t="s">
+        <v>110</v>
+      </c>
+      <c r="T28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F29" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G29">
-        <v>92.47697847418542</v>
+        <v>99.37874741911503</v>
       </c>
       <c r="H29">
-        <v>112.7116775791235</v>
+        <v>119.6134465240531</v>
       </c>
       <c r="I29">
-        <v>124.2185433507283</v>
+        <v>131.1203122956579</v>
       </c>
       <c r="J29">
         <v>120</v>
@@ -2144,40 +2489,52 @@
       <c r="N29">
         <v>29.65282857134476</v>
       </c>
-      <c r="O29" t="s">
-        <v>106</v>
-      </c>
-      <c r="P29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <v>92.47697847418542</v>
+      </c>
+      <c r="Q29">
+        <v>112.7116775791235</v>
+      </c>
+      <c r="R29">
+        <v>124.2185433507283</v>
+      </c>
+      <c r="S29" t="s">
+        <v>110</v>
+      </c>
+      <c r="T29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G30">
-        <v>99.17377697095665</v>
+        <v>99.67156283279211</v>
       </c>
       <c r="H30">
-        <v>117.9565912525574</v>
+        <v>118.4543771143929</v>
       </c>
       <c r="I30">
-        <v>127.314183311936</v>
+        <v>127.8119691737715</v>
       </c>
       <c r="J30">
         <v>180</v>
@@ -2194,40 +2551,52 @@
       <c r="N30">
         <v>16.90331528315725</v>
       </c>
-      <c r="O30" t="s">
-        <v>106</v>
-      </c>
-      <c r="P30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="O30">
+        <v>2</v>
+      </c>
+      <c r="P30">
+        <v>109.079451822505</v>
+      </c>
+      <c r="Q30">
+        <v>127.8622661041058</v>
+      </c>
+      <c r="R30">
+        <v>137.2198581634844</v>
+      </c>
+      <c r="S30" t="s">
+        <v>111</v>
+      </c>
+      <c r="T30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G31">
-        <v>100.3745505433642</v>
+        <v>103.4711714084155</v>
       </c>
       <c r="H31">
-        <v>119.1393856984831</v>
+        <v>122.2360065635344</v>
       </c>
       <c r="I31">
-        <v>128.5178875202687</v>
+        <v>131.61450838532</v>
       </c>
       <c r="J31">
         <v>180</v>
@@ -2244,40 +2613,52 @@
       <c r="N31">
         <v>17.34211485240496</v>
       </c>
-      <c r="O31" t="s">
-        <v>106</v>
-      </c>
-      <c r="P31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="O31">
+        <v>2</v>
+      </c>
+      <c r="P31">
+        <v>110.2802253949126</v>
+      </c>
+      <c r="Q31">
+        <v>129.0450605500315</v>
+      </c>
+      <c r="R31">
+        <v>138.4235623718171</v>
+      </c>
+      <c r="S31" t="s">
+        <v>110</v>
+      </c>
+      <c r="T31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G32">
-        <v>105.6897482914424</v>
+        <v>108.6769417160876</v>
       </c>
       <c r="H32">
-        <v>119.7398839550779</v>
+        <v>122.7270773797231</v>
       </c>
       <c r="I32">
-        <v>124.3837973964911</v>
+        <v>127.3709908211363</v>
       </c>
       <c r="J32">
         <v>180</v>
@@ -2294,40 +2675,52 @@
       <c r="N32">
         <v>17.22071755144147</v>
       </c>
-      <c r="O32" t="s">
-        <v>108</v>
-      </c>
-      <c r="P32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="O32">
+        <v>2</v>
+      </c>
+      <c r="P32">
+        <v>108.6769417160876</v>
+      </c>
+      <c r="Q32">
+        <v>122.7270773797231</v>
+      </c>
+      <c r="R32">
+        <v>127.3709908211363</v>
+      </c>
+      <c r="S32" t="s">
+        <v>109</v>
+      </c>
+      <c r="T32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E33" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F33" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G33">
-        <v>111.3818220273667</v>
+        <v>122.9843844240387</v>
       </c>
       <c r="H33">
-        <v>126.7800734387346</v>
+        <v>138.3826358354066</v>
       </c>
       <c r="I33">
-        <v>132.0721581834358</v>
+        <v>143.6747205801078</v>
       </c>
       <c r="J33">
         <v>180</v>
@@ -2344,40 +2737,52 @@
       <c r="N33">
         <v>22.17402235901627</v>
       </c>
-      <c r="O33" t="s">
-        <v>107</v>
-      </c>
-      <c r="P33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="O33">
+        <v>2</v>
+      </c>
+      <c r="P33">
+        <v>106.3049439214151</v>
+      </c>
+      <c r="Q33">
+        <v>121.703195332783</v>
+      </c>
+      <c r="R33">
+        <v>126.9952800774842</v>
+      </c>
+      <c r="S33" t="s">
+        <v>109</v>
+      </c>
+      <c r="T33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G34">
-        <v>107.4318138500012</v>
+        <v>124.7529630936472</v>
       </c>
       <c r="H34">
-        <v>128.8393511384311</v>
+        <v>146.1605003820771</v>
       </c>
       <c r="I34">
-        <v>140.9811106490832</v>
+        <v>158.3022598927292</v>
       </c>
       <c r="J34">
         <v>180</v>
@@ -2394,40 +2799,52 @@
       <c r="N34">
         <v>26.79734157293274</v>
       </c>
-      <c r="O34" t="s">
-        <v>106</v>
-      </c>
-      <c r="P34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="O34">
+        <v>2</v>
+      </c>
+      <c r="P34">
+        <v>124.7529630936472</v>
+      </c>
+      <c r="Q34">
+        <v>146.1605003820771</v>
+      </c>
+      <c r="R34">
+        <v>158.3022598927292</v>
+      </c>
+      <c r="S34" t="s">
+        <v>111</v>
+      </c>
+      <c r="T34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F35" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G35">
-        <v>106.8363035495291</v>
+        <v>106.3286151961343</v>
       </c>
       <c r="H35">
-        <v>124.6191178311298</v>
+        <v>124.111429477735</v>
       </c>
       <c r="I35">
-        <v>133.9767098905084</v>
+        <v>133.4690215371136</v>
       </c>
       <c r="J35">
         <v>180</v>
@@ -2444,40 +2861,52 @@
       <c r="N35">
         <v>16.78832334705435</v>
       </c>
-      <c r="O35" t="s">
-        <v>106</v>
-      </c>
-      <c r="P35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>116.7419784010775</v>
+      </c>
+      <c r="Q35">
+        <v>134.5247926826782</v>
+      </c>
+      <c r="R35">
+        <v>143.8823847420568</v>
+      </c>
+      <c r="S35" t="s">
+        <v>111</v>
+      </c>
+      <c r="T35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F36" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G36">
-        <v>115.4203696987749</v>
+        <v>118.3261541474113</v>
       </c>
       <c r="H36">
-        <v>133.2031839803757</v>
+        <v>136.1089684290122</v>
       </c>
       <c r="I36">
-        <v>142.5607760397542</v>
+        <v>145.4665604883906</v>
       </c>
       <c r="J36">
         <v>180</v>
@@ -2494,40 +2923,52 @@
       <c r="N36">
         <v>16.78832334705435</v>
       </c>
-      <c r="O36" t="s">
-        <v>106</v>
-      </c>
-      <c r="P36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="P36">
+        <v>125.3260445503233</v>
+      </c>
+      <c r="Q36">
+        <v>143.1088588319241</v>
+      </c>
+      <c r="R36">
+        <v>152.4664508913026</v>
+      </c>
+      <c r="S36" t="s">
+        <v>111</v>
+      </c>
+      <c r="T36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F37" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G37">
-        <v>127.314183311936</v>
+        <v>127.8119691737715</v>
       </c>
       <c r="H37">
-        <v>147.7325048230146</v>
+        <v>148.2302906848501</v>
       </c>
       <c r="I37">
-        <v>159.7528263340933</v>
+        <v>160.2506121959288</v>
       </c>
       <c r="J37">
         <v>180</v>
@@ -2544,40 +2985,52 @@
       <c r="N37">
         <v>19.440198958216</v>
       </c>
-      <c r="O37" t="s">
-        <v>106</v>
-      </c>
-      <c r="P37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16">
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>137.2198581634844</v>
+      </c>
+      <c r="Q37">
+        <v>157.638179674563</v>
+      </c>
+      <c r="R37">
+        <v>169.6585011856417</v>
+      </c>
+      <c r="S37" t="s">
+        <v>110</v>
+      </c>
+      <c r="T37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G38">
-        <v>128.5178875202687</v>
+        <v>131.61450838532</v>
       </c>
       <c r="H38">
-        <v>150.4870640742519</v>
+        <v>153.5836849393032</v>
       </c>
       <c r="I38">
-        <v>164.0680184060128</v>
+        <v>167.1646392710641</v>
       </c>
       <c r="J38">
         <v>180</v>
@@ -2594,40 +3047,52 @@
       <c r="N38">
         <v>20.34535693147248</v>
       </c>
-      <c r="O38" t="s">
-        <v>106</v>
-      </c>
-      <c r="P38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16">
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38">
+        <v>138.4235623718171</v>
+      </c>
+      <c r="Q38">
+        <v>160.3927389258003</v>
+      </c>
+      <c r="R38">
+        <v>173.9736932575612</v>
+      </c>
+      <c r="S38" t="s">
+        <v>110</v>
+      </c>
+      <c r="T38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E39" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F39" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G39">
-        <v>144.2174985950932</v>
+        <v>144.7152844569287</v>
       </c>
       <c r="H39">
-        <v>158.7787806946488</v>
+        <v>159.2765665564843</v>
       </c>
       <c r="I39">
-        <v>165.0479516830933</v>
+        <v>165.5457375449288</v>
       </c>
       <c r="J39">
         <v>180</v>
@@ -2644,40 +3109,52 @@
       <c r="N39">
         <v>13.42643586024874</v>
       </c>
-      <c r="O39" t="s">
-        <v>106</v>
-      </c>
-      <c r="P39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39">
+        <v>154.1231734466416</v>
+      </c>
+      <c r="Q39">
+        <v>168.6844555461972</v>
+      </c>
+      <c r="R39">
+        <v>174.9536265346417</v>
+      </c>
+      <c r="S39" t="s">
+        <v>109</v>
+      </c>
+      <c r="T39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F40" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G40">
-        <v>124.3837973964911</v>
+        <v>134.0279476009105</v>
       </c>
       <c r="H40">
-        <v>141.0540228057363</v>
+        <v>150.6981730101556</v>
       </c>
       <c r="I40">
-        <v>149.4695815483147</v>
+        <v>159.1137317527341</v>
       </c>
       <c r="J40">
         <v>180</v>
@@ -2694,40 +3171,52 @@
       <c r="N40">
         <v>20.52918936489361</v>
       </c>
-      <c r="O40" t="s">
-        <v>106</v>
-      </c>
-      <c r="P40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40">
+        <v>134.0279476009105</v>
+      </c>
+      <c r="Q40">
+        <v>150.6981730101556</v>
+      </c>
+      <c r="R40">
+        <v>159.1137317527341</v>
+      </c>
+      <c r="S40" t="s">
+        <v>111</v>
+      </c>
+      <c r="T40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G41">
-        <v>145.8600023726736</v>
+        <v>148.9566232377249</v>
       </c>
       <c r="H41">
-        <v>167.6226588250524</v>
+        <v>170.7192796901037</v>
       </c>
       <c r="I41">
-        <v>181.0444263885422</v>
+        <v>184.1410472535935</v>
       </c>
       <c r="J41">
         <v>180</v>
@@ -2744,40 +3233,52 @@
       <c r="N41">
         <v>20.64223687015227</v>
       </c>
-      <c r="O41" t="s">
-        <v>106</v>
-      </c>
-      <c r="P41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41">
+        <v>155.765677224222</v>
+      </c>
+      <c r="Q41">
+        <v>177.5283336766009</v>
+      </c>
+      <c r="R41">
+        <v>190.9501012400906</v>
+      </c>
+      <c r="S41" t="s">
+        <v>111</v>
+      </c>
+      <c r="T41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E42" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F42" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G42">
-        <v>126.1289043240826</v>
+        <v>136.8786262223814</v>
       </c>
       <c r="H42">
-        <v>145.6436072990093</v>
+        <v>156.3933291973081</v>
       </c>
       <c r="I42">
-        <v>156.6363102739359</v>
+        <v>167.3860321722347</v>
       </c>
       <c r="J42">
         <v>180</v>
@@ -2794,40 +3295,52 @@
       <c r="N42">
         <v>30.53056448142775</v>
       </c>
-      <c r="O42" t="s">
-        <v>106</v>
-      </c>
-      <c r="P42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42">
+        <v>124.2185433507283</v>
+      </c>
+      <c r="Q42">
+        <v>143.733246325655</v>
+      </c>
+      <c r="R42">
+        <v>154.7259493005816</v>
+      </c>
+      <c r="S42" t="s">
+        <v>111</v>
+      </c>
+      <c r="T42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D43" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F43" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G43">
-        <v>159.7528263340933</v>
+        <v>160.2506121959288</v>
       </c>
       <c r="H43">
-        <v>182.1773262727881</v>
+        <v>182.6751121346236</v>
       </c>
       <c r="I43">
-        <v>196.3360484337051</v>
+        <v>196.8338342955406</v>
       </c>
       <c r="J43">
         <v>240</v>
@@ -2844,40 +3357,52 @@
       <c r="N43">
         <v>19.94872317416675</v>
       </c>
-      <c r="O43" t="s">
-        <v>106</v>
-      </c>
-      <c r="P43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43">
+        <v>169.6585011856417</v>
+      </c>
+      <c r="Q43">
+        <v>192.0830011243365</v>
+      </c>
+      <c r="R43">
+        <v>206.2417232852535</v>
+      </c>
+      <c r="S43" t="s">
+        <v>111</v>
+      </c>
+      <c r="T43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F44" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G44">
-        <v>140.9811106490832</v>
+        <v>158.3022598927292</v>
       </c>
       <c r="H44">
-        <v>160.7987172745242</v>
+        <v>178.1198665181702</v>
       </c>
       <c r="I44">
-        <v>172.2281016777429</v>
+        <v>189.5492509213889</v>
       </c>
       <c r="J44">
         <v>240</v>
@@ -2894,40 +3419,52 @@
       <c r="N44">
         <v>25.84246349846404</v>
       </c>
-      <c r="O44" t="s">
-        <v>106</v>
-      </c>
-      <c r="P44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44">
+        <v>158.3022598927292</v>
+      </c>
+      <c r="Q44">
+        <v>178.1198665181702</v>
+      </c>
+      <c r="R44">
+        <v>189.5492509213889</v>
+      </c>
+      <c r="S44" t="s">
+        <v>110</v>
+      </c>
+      <c r="T44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F45" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G45">
-        <v>149.4695815483147</v>
+        <v>159.1137317527341</v>
       </c>
       <c r="H45">
-        <v>165.7796144944438</v>
+        <v>175.4237646988632</v>
       </c>
       <c r="I45">
-        <v>173.6644252183506</v>
+        <v>183.30857542277</v>
       </c>
       <c r="J45">
         <v>240</v>
@@ -2944,40 +3481,52 @@
       <c r="N45">
         <v>21.37953689765456</v>
       </c>
-      <c r="O45" t="s">
-        <v>106</v>
-      </c>
-      <c r="P45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="O45">
+        <v>1</v>
+      </c>
+      <c r="P45">
+        <v>159.1137317527341</v>
+      </c>
+      <c r="Q45">
+        <v>175.4237646988632</v>
+      </c>
+      <c r="R45">
+        <v>183.30857542277</v>
+      </c>
+      <c r="S45" t="s">
+        <v>111</v>
+      </c>
+      <c r="T45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G46">
-        <v>172.2281016777429</v>
+        <v>183.30857542277</v>
       </c>
       <c r="H46">
-        <v>191.7381298013266</v>
+        <v>202.8186035463537</v>
       </c>
       <c r="I46">
-        <v>202.9072690360213</v>
+        <v>213.9877427810484</v>
       </c>
       <c r="J46">
         <v>240</v>
@@ -2994,40 +3543,52 @@
       <c r="N46">
         <v>26.13659157001889</v>
       </c>
-      <c r="O46" t="s">
-        <v>106</v>
-      </c>
-      <c r="P46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="P46">
+        <v>183.30857542277</v>
+      </c>
+      <c r="Q46">
+        <v>202.8186035463537</v>
+      </c>
+      <c r="R46">
+        <v>213.9877427810484</v>
+      </c>
+      <c r="S46" t="s">
+        <v>111</v>
+      </c>
+      <c r="T46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E47" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F47" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G47">
-        <v>141.3544453071501</v>
+        <v>152.9570077038221</v>
       </c>
       <c r="H47">
-        <v>158.4133944246702</v>
+        <v>170.0159568213422</v>
       </c>
       <c r="I47">
-        <v>166.5428435421902</v>
+        <v>178.1454059388622</v>
       </c>
       <c r="J47">
         <v>240</v>
@@ -3044,40 +3605,52 @@
       <c r="N47">
         <v>28.04663758277022</v>
       </c>
-      <c r="O47" t="s">
-        <v>106</v>
-      </c>
-      <c r="P47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
+      <c r="O47">
+        <v>1</v>
+      </c>
+      <c r="P47">
+        <v>136.2775672011985</v>
+      </c>
+      <c r="Q47">
+        <v>153.3365163187186</v>
+      </c>
+      <c r="R47">
+        <v>161.4659654362386</v>
+      </c>
+      <c r="S47" t="s">
+        <v>110</v>
+      </c>
+      <c r="T47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D48" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F48" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G48">
-        <v>156.6363102739359</v>
+        <v>167.3860321722347</v>
       </c>
       <c r="H48">
-        <v>170.5963788323518</v>
+        <v>181.3461007306506</v>
       </c>
       <c r="I48">
-        <v>175.5971140574344</v>
+        <v>186.3468359557332</v>
       </c>
       <c r="J48">
         <v>240</v>
@@ -3094,40 +3667,52 @@
       <c r="N48">
         <v>21.47950892254682</v>
       </c>
-      <c r="O48" t="s">
-        <v>108</v>
-      </c>
-      <c r="P48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16">
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="P48">
+        <v>154.7259493005816</v>
+      </c>
+      <c r="Q48">
+        <v>168.6860178589975</v>
+      </c>
+      <c r="R48">
+        <v>173.6867530840801</v>
+      </c>
+      <c r="S48" t="s">
+        <v>109</v>
+      </c>
+      <c r="T48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D49" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F49" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G49">
-        <v>164.0680184060128</v>
+        <v>165.5457375449288</v>
       </c>
       <c r="H49">
-        <v>184.0073603858499</v>
+        <v>185.4850795247659</v>
       </c>
       <c r="I49">
-        <v>195.8320356990204</v>
+        <v>197.3097548379364</v>
       </c>
       <c r="J49">
         <v>240</v>
@@ -3144,14 +3729,26 @@
       <c r="N49">
         <v>18.0343453484478</v>
       </c>
-      <c r="O49" t="s">
-        <v>106</v>
-      </c>
-      <c r="P49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16">
+      <c r="O49">
+        <v>1</v>
+      </c>
+      <c r="P49">
+        <v>173.9736932575612</v>
+      </c>
+      <c r="Q49">
+        <v>193.9130352373983</v>
+      </c>
+      <c r="R49">
+        <v>205.7377105505688</v>
+      </c>
+      <c r="S49" t="s">
+        <v>111</v>
+      </c>
+      <c r="T49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3159,25 +3756,25 @@
         <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F50" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G50">
-        <v>178.4743875433421</v>
+        <v>178.9721734051776</v>
       </c>
       <c r="H50">
-        <v>196.2572018249429</v>
+        <v>196.7549876867784</v>
       </c>
       <c r="I50">
-        <v>205.6147938843214</v>
+        <v>206.1125797461569</v>
       </c>
       <c r="J50">
         <v>300</v>
@@ -3194,11 +3791,23 @@
       <c r="N50">
         <v>16.51002353530952</v>
       </c>
-      <c r="O50" t="s">
-        <v>106</v>
-      </c>
-      <c r="P50" t="b">
-        <v>0</v>
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50">
+        <v>188.3800623948905</v>
+      </c>
+      <c r="Q50">
+        <v>206.1628766764913</v>
+      </c>
+      <c r="R50">
+        <v>215.5204687358698</v>
+      </c>
+      <c r="S50" t="s">
+        <v>111</v>
+      </c>
+      <c r="T50" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/结果/问题三_运输调度_修复版.xlsx
+++ b/结果/问题三_运输调度_修复版.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="108">
   <si>
     <t>mission_id</t>
   </si>
@@ -79,18 +79,18 @@
     <t>UC01</t>
   </si>
   <si>
+    <t>UC02</t>
+  </si>
+  <si>
+    <t>UA01</t>
+  </si>
+  <si>
     <t>UB01</t>
   </si>
   <si>
-    <t>UA01</t>
-  </si>
-  <si>
     <t>UB02</t>
   </si>
   <si>
-    <t>UC02</t>
-  </si>
-  <si>
     <t>UA02</t>
   </si>
   <si>
@@ -103,54 +103,54 @@
     <t>C</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>C-BAT-01</t>
   </si>
   <si>
+    <t>C-BAT-02</t>
+  </si>
+  <si>
+    <t>C-BAT-03</t>
+  </si>
+  <si>
+    <t>A-BAT-01</t>
+  </si>
+  <si>
     <t>B-BAT-01</t>
   </si>
   <si>
-    <t>A-BAT-01</t>
-  </si>
-  <si>
     <t>B-BAT-02</t>
   </si>
   <si>
+    <t>A-BAT-02</t>
+  </si>
+  <si>
+    <t>A-BAT-03</t>
+  </si>
+  <si>
+    <t>A-BAT-04</t>
+  </si>
+  <si>
+    <t>A-BAT-05</t>
+  </si>
+  <si>
+    <t>A-BAT-06</t>
+  </si>
+  <si>
     <t>B-BAT-03</t>
   </si>
   <si>
+    <t>C-BAT-04</t>
+  </si>
+  <si>
     <t>B-BAT-04</t>
   </si>
   <si>
-    <t>C-BAT-02</t>
-  </si>
-  <si>
-    <t>A-BAT-02</t>
-  </si>
-  <si>
-    <t>C-BAT-03</t>
-  </si>
-  <si>
-    <t>C-BAT-04</t>
-  </si>
-  <si>
-    <t>A-BAT-03</t>
-  </si>
-  <si>
-    <t>A-BAT-04</t>
-  </si>
-  <si>
-    <t>A-BAT-05</t>
-  </si>
-  <si>
-    <t>A-BAT-06</t>
-  </si>
-  <si>
     <t>S001</t>
   </si>
   <si>
@@ -178,12 +178,12 @@
     <t>S003</t>
   </si>
   <si>
+    <t>S008</t>
+  </si>
+  <si>
     <t>S004</t>
   </si>
   <si>
-    <t>S008</t>
-  </si>
-  <si>
     <t>S015</t>
   </si>
   <si>
@@ -199,16 +199,13 @@
     <t>S001-WAT-01,S001-WAT-02,S001-WAT-03,S001-WAT-04,S001-WAT-05,S001-MED-01,S001-MED-02</t>
   </si>
   <si>
+    <t>S002-WAT-01,S002-WAT-02,S002-WAT-03,S002-WAT-04,S002-MED-01</t>
+  </si>
+  <si>
     <t>S001-WAT-06,S001-WAT-07,S001-WAT-08</t>
   </si>
   <si>
-    <t>S002-WAT-01,S002-MED-01</t>
-  </si>
-  <si>
-    <t>S006-WAT-01,S006-WAT-02</t>
-  </si>
-  <si>
-    <t>S006-WAT-03,S006-MED-01</t>
+    <t>S006-WAT-01,S006-MED-01</t>
   </si>
   <si>
     <t>S007-WAT-01,S007-WAT-02</t>
@@ -226,13 +223,10 @@
     <t>S014-WAT-01,S014-MED-01</t>
   </si>
   <si>
-    <t>S002-WAT-02</t>
-  </si>
-  <si>
-    <t>S002-WAT-03</t>
-  </si>
-  <si>
-    <t>S002-WAT-04</t>
+    <t>S006-WAT-02</t>
+  </si>
+  <si>
+    <t>S006-WAT-03</t>
   </si>
   <si>
     <t>S007-MED-01</t>
@@ -241,7 +235,7 @@
     <t>S003-WAT-01,S003-WAT-02,S003-WAT-03,S003-WAT-04,S003-MED-01</t>
   </si>
   <si>
-    <t>S001-FOD-01,S001-FOD-02,S001-FOD-03</t>
+    <t>S008-WAT-01,S008-WAT-02,S008-MED-01</t>
   </si>
   <si>
     <t>S004-WAT-01,S004-WAT-02</t>
@@ -250,18 +244,18 @@
     <t>S004-WAT-03,S004-MED-01</t>
   </si>
   <si>
-    <t>S008-WAT-01,S008-MED-01</t>
+    <t>S001-FOD-01,S001-FOD-02</t>
   </si>
   <si>
     <t>S002-FOD-01,S002-FOD-02</t>
   </si>
   <si>
-    <t>S008-WAT-02</t>
-  </si>
-  <si>
     <t>S015-MED-01</t>
   </si>
   <si>
+    <t>S001-FOD-03</t>
+  </si>
+  <si>
     <t>S006-FOD-01</t>
   </si>
   <si>
@@ -280,7 +274,7 @@
     <t>S014-FOD-01</t>
   </si>
   <si>
-    <t>S005-WAT-01,S005-MED-01</t>
+    <t>S005-WAT-01,S005-WAT-02,S005-WAT-03,S005-MED-01</t>
   </si>
   <si>
     <t>S009-WAT-01,S009-MED-01</t>
@@ -293,12 +287,6 @@
   </si>
   <si>
     <t>S003-FOD-01,S003-FOD-02</t>
-  </si>
-  <si>
-    <t>S005-WAT-02</t>
-  </si>
-  <si>
-    <t>S005-WAT-03</t>
   </si>
   <si>
     <t>S002-HYG-01</t>
@@ -707,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T50"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -828,7 +816,7 @@
         <v>26.19033615606908</v>
       </c>
       <c r="S2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -842,25 +830,25 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
         <v>61</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H3">
-        <v>15.37289355636781</v>
+        <v>33.60645317486046</v>
       </c>
       <c r="I3">
-        <v>20.30834266829118</v>
+        <v>43.96023149817256</v>
       </c>
       <c r="J3">
         <v>60</v>
@@ -869,28 +857,28 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1.063798065282268</v>
+        <v>5.151810515822099</v>
       </c>
       <c r="M3">
-        <v>0.734050483679433</v>
+        <v>0.3560236855222376</v>
       </c>
       <c r="N3">
-        <v>18.79409713814971</v>
+        <v>37.14358913391919</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>15.37289355636781</v>
+        <v>23.70077832331209</v>
       </c>
       <c r="R3">
-        <v>20.30834266829118</v>
+        <v>34.05455664662419</v>
       </c>
       <c r="S3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -901,28 +889,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
       </c>
       <c r="G4">
-        <v>9.905674851548365</v>
+        <v>26.19033615606908</v>
       </c>
       <c r="H4">
-        <v>31.32399636262702</v>
+        <v>42.68858756743695</v>
       </c>
       <c r="I4">
-        <v>43.34431787370568</v>
+        <v>47.98067231213816</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -931,28 +919,28 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.421359503464448</v>
+        <v>2.066398756230736</v>
       </c>
       <c r="M4">
-        <v>0.4619201103412338</v>
+        <v>0.741700155471158</v>
       </c>
       <c r="N4">
-        <v>19.9917309426066</v>
+        <v>23.21638327465262</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>9.905674851548365</v>
+        <v>26.19033615606908</v>
       </c>
       <c r="Q4">
-        <v>31.32399636262702</v>
+        <v>42.68858756743695</v>
       </c>
       <c r="R4">
-        <v>43.34431787370568</v>
+        <v>47.98067231213816</v>
       </c>
       <c r="S4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T4" t="b">
         <v>1</v>
@@ -963,7 +951,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
@@ -981,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>14.67766295665795</v>
+        <v>15.56128209955562</v>
       </c>
       <c r="I5">
-        <v>20.06321480220478</v>
+        <v>21.83045308800013</v>
       </c>
       <c r="J5">
         <v>60</v>
@@ -993,13 +981,13 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1.087081446911481</v>
+        <v>1.106805665390136</v>
       </c>
       <c r="M5">
-        <v>0.7282296382721298</v>
+        <v>0.7540431854688587</v>
       </c>
       <c r="N5">
-        <v>18.96225489436069</v>
+        <v>13.66239764817473</v>
       </c>
       <c r="O5">
         <v>2</v>
@@ -1008,13 +996,13 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>14.67766295665795</v>
+        <v>15.56128209955562</v>
       </c>
       <c r="R5">
-        <v>20.06321480220478</v>
+        <v>21.83045308800013</v>
       </c>
       <c r="S5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -1028,25 +1016,25 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
       </c>
       <c r="G6">
-        <v>20.06321480220478</v>
+        <v>7.323532094892318</v>
       </c>
       <c r="H6">
-        <v>34.74087775886273</v>
+        <v>24.99375750413748</v>
       </c>
       <c r="I6">
-        <v>40.12642960440956</v>
+        <v>33.40931624671596</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -1055,28 +1043,28 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>0.9613264853346692</v>
+        <v>1.60089897336792</v>
       </c>
       <c r="M6">
-        <v>0.7596683786663327</v>
+        <v>0.5997752566580201</v>
       </c>
       <c r="N6">
-        <v>18.05402461630594</v>
+        <v>22.67315925210164</v>
       </c>
       <c r="O6">
         <v>2</v>
       </c>
       <c r="P6">
-        <v>20.06321480220478</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>34.74087775886273</v>
+        <v>17.67022540924516</v>
       </c>
       <c r="R6">
-        <v>40.12642960440956</v>
+        <v>26.08578415182364</v>
       </c>
       <c r="S6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T6" t="b">
         <v>1</v>
@@ -1087,28 +1075,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
         <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
       </c>
       <c r="G7">
-        <v>20.30834266829118</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H7">
-        <v>37.97856807753634</v>
+        <v>26.92317826681158</v>
       </c>
       <c r="I7">
-        <v>46.39412682011481</v>
+        <v>34.68945945985256</v>
       </c>
       <c r="J7">
         <v>60</v>
@@ -1117,28 +1105,28 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1.60089897336792</v>
+        <v>1.424415898434041</v>
       </c>
       <c r="M7">
-        <v>0.5997752566580201</v>
+        <v>0.6438960253914898</v>
       </c>
       <c r="N7">
-        <v>22.67315925210164</v>
+        <v>21.39855926646807</v>
       </c>
       <c r="O7">
         <v>2</v>
       </c>
       <c r="P7">
-        <v>20.30834266829118</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>37.97856807753634</v>
+        <v>17.01750341526321</v>
       </c>
       <c r="R7">
-        <v>46.39412682011481</v>
+        <v>24.7837846083042</v>
       </c>
       <c r="S7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T7" t="b">
         <v>1</v>
@@ -1149,16 +1137,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
         <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>66</v>
@@ -1167,10 +1155,10 @@
         <v>9.905674851548365</v>
       </c>
       <c r="H8">
-        <v>28.09110245175328</v>
+        <v>27.9464117111378</v>
       </c>
       <c r="I8">
-        <v>36.44969671862485</v>
+        <v>36.73603745961613</v>
       </c>
       <c r="J8">
         <v>60</v>
@@ -1179,28 +1167,28 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <v>2.910315433999106</v>
+        <v>1.637365079674389</v>
       </c>
       <c r="M8">
-        <v>0.6362105707501118</v>
+        <v>0.6361410934056912</v>
       </c>
       <c r="N8">
-        <v>27.0257293895793</v>
+        <v>16.21694297621002</v>
       </c>
       <c r="O8">
         <v>2</v>
       </c>
       <c r="P8">
-        <v>9.905674851548365</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>28.09110245175328</v>
+        <v>18.04073685958943</v>
       </c>
       <c r="R8">
-        <v>36.44969671862485</v>
+        <v>26.83036260806776</v>
       </c>
       <c r="S8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -1211,16 +1199,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
         <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
         <v>67</v>
@@ -1229,10 +1217,10 @@
         <v>9.905674851548365</v>
       </c>
       <c r="H9">
-        <v>27.9464117111378</v>
+        <v>32.14420882468487</v>
       </c>
       <c r="I9">
-        <v>36.73603745961613</v>
+        <v>45.05174279782136</v>
       </c>
       <c r="J9">
         <v>60</v>
@@ -1241,28 +1229,28 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1.637365079674389</v>
+        <v>2.471325003399136</v>
       </c>
       <c r="M9">
-        <v>0.6361410934056912</v>
+        <v>0.4508166659113031</v>
       </c>
       <c r="N9">
-        <v>16.21694297621002</v>
+        <v>20.23230557192176</v>
       </c>
       <c r="O9">
         <v>2</v>
       </c>
       <c r="P9">
-        <v>9.905674851548365</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>27.9464117111378</v>
+        <v>22.2385339731365</v>
       </c>
       <c r="R9">
-        <v>36.73603745961613</v>
+        <v>35.146067946273</v>
       </c>
       <c r="S9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -1273,28 +1261,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
         <v>68</v>
       </c>
       <c r="G10">
-        <v>26.19033615606908</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H10">
-        <v>47.61045803875672</v>
+        <v>31.12234688112371</v>
       </c>
       <c r="I10">
-        <v>59.08407992144435</v>
+        <v>43.0871300218102</v>
       </c>
       <c r="J10">
         <v>60</v>
@@ -1303,28 +1291,28 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>4.320888294761101</v>
+        <v>1.974536954059142</v>
       </c>
       <c r="M10">
-        <v>0.4598889631548624</v>
+        <v>0.5612140102090795</v>
       </c>
       <c r="N10">
-        <v>33.39289855274107</v>
+        <v>17.84036311213661</v>
       </c>
       <c r="O10">
         <v>2</v>
       </c>
       <c r="P10">
-        <v>26.19033615606908</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>47.61045803875672</v>
+        <v>21.21667202957535</v>
       </c>
       <c r="R10">
-        <v>59.08407992144435</v>
+        <v>33.18145517026183</v>
       </c>
       <c r="S10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T10" t="b">
         <v>1</v>
@@ -1335,28 +1323,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
         <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
         <v>69</v>
       </c>
       <c r="G11">
-        <v>36.44969671862485</v>
+        <v>21.83045308800013</v>
       </c>
       <c r="H11">
-        <v>57.78439582356296</v>
+        <v>36.39173518755575</v>
       </c>
       <c r="I11">
-        <v>69.29126159516773</v>
+        <v>42.66090617600025</v>
       </c>
       <c r="J11">
         <v>60</v>
@@ -1365,28 +1353,28 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>3.58861224407448</v>
+        <v>1.092476706316119</v>
       </c>
       <c r="M11">
-        <v>0.55142346949069</v>
+        <v>0.757227398596418</v>
       </c>
       <c r="N11">
-        <v>30.0874858239473</v>
+        <v>13.59340636374428</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <v>9.905674851548365</v>
+        <v>21.83045308800013</v>
       </c>
       <c r="Q11">
-        <v>31.24037395648647</v>
+        <v>36.39173518755575</v>
       </c>
       <c r="R11">
-        <v>42.74723972809124</v>
+        <v>42.66090617600025</v>
       </c>
       <c r="S11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T11" t="b">
         <v>1</v>
@@ -1397,28 +1385,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
         <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
         <v>70</v>
       </c>
       <c r="G12">
-        <v>9.905674851548365</v>
+        <v>36.73603745961613</v>
       </c>
       <c r="H12">
-        <v>30.32399636262702</v>
+        <v>51.29731955917176</v>
       </c>
       <c r="I12">
-        <v>42.34431787370568</v>
+        <v>57.56649054761626</v>
       </c>
       <c r="J12">
         <v>60</v>
@@ -1427,28 +1415,28 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <v>2.38786730414774</v>
+        <v>1.092476706316119</v>
       </c>
       <c r="M12">
-        <v>0.4693628213005021</v>
+        <v>0.757227398596418</v>
       </c>
       <c r="N12">
-        <v>19.83047220515579</v>
+        <v>13.59340636374428</v>
       </c>
       <c r="O12">
         <v>1</v>
       </c>
       <c r="P12">
-        <v>9.905674851548365</v>
+        <v>26.83036260806776</v>
       </c>
       <c r="Q12">
-        <v>30.32399636262702</v>
+        <v>41.39164470762339</v>
       </c>
       <c r="R12">
-        <v>42.34431787370568</v>
+        <v>47.66081569606789</v>
       </c>
       <c r="S12" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T12" t="b">
         <v>1</v>
@@ -1459,7 +1447,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
@@ -1468,19 +1456,19 @@
         <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
         <v>71</v>
       </c>
       <c r="G13">
-        <v>9.905674851548365</v>
+        <v>33.40931624671596</v>
       </c>
       <c r="H13">
-        <v>30.32399636262702</v>
+        <v>50.07954165596111</v>
       </c>
       <c r="I13">
-        <v>42.34431787370568</v>
+        <v>58.49510039853959</v>
       </c>
       <c r="J13">
         <v>60</v>
@@ -1489,28 +1477,28 @@
         <v>1</v>
       </c>
       <c r="L13">
-        <v>2.38786730414774</v>
+        <v>1.278665737006417</v>
       </c>
       <c r="M13">
-        <v>0.4693628213005021</v>
+        <v>0.6803335657483958</v>
       </c>
       <c r="N13">
-        <v>19.83047220515579</v>
+        <v>20.34591921171301</v>
       </c>
       <c r="O13">
         <v>1</v>
       </c>
       <c r="P13">
-        <v>36.73603745961613</v>
+        <v>24.7837846083042</v>
       </c>
       <c r="Q13">
-        <v>57.15435897069479</v>
+        <v>41.45401001754935</v>
       </c>
       <c r="R13">
-        <v>69.17468048177344</v>
+        <v>49.86956876012783</v>
       </c>
       <c r="S13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T13" t="b">
         <v>1</v>
@@ -1521,58 +1509,58 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
         <v>72</v>
       </c>
       <c r="G14">
-        <v>36.73603745961613</v>
+        <v>43.96023149817256</v>
       </c>
       <c r="H14">
-        <v>57.15435897069479</v>
+        <v>70.20848545797438</v>
       </c>
       <c r="I14">
-        <v>69.17468048177344</v>
+        <v>83.30807275110952</v>
       </c>
       <c r="J14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14">
-        <v>2.38786730414774</v>
+        <v>5.440500810633867</v>
       </c>
       <c r="M14">
-        <v>0.4693628213005021</v>
+        <v>0.3199373986707666</v>
       </c>
       <c r="N14">
-        <v>19.83047220515579</v>
+        <v>38.44670504800009</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>42.34431787370568</v>
+        <v>34.05455664662419</v>
       </c>
       <c r="Q14">
-        <v>62.76263938478434</v>
+        <v>60.30281060642601</v>
       </c>
       <c r="R14">
-        <v>74.78296089586298</v>
+        <v>73.40239789956115</v>
       </c>
       <c r="S14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T14" t="b">
         <v>1</v>
@@ -1583,58 +1571,58 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
         <v>73</v>
       </c>
       <c r="G15">
-        <v>40.12642960440956</v>
+        <v>51.62987554632826</v>
       </c>
       <c r="H15">
-        <v>56.79665501365471</v>
+        <v>74.37264188394303</v>
       </c>
       <c r="I15">
-        <v>65.21221375623318</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="J15">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15">
-        <v>1.278665737006417</v>
+        <v>4.880456740806956</v>
       </c>
       <c r="M15">
-        <v>0.6803335657483958</v>
+        <v>0.3899429073991305</v>
       </c>
       <c r="N15">
-        <v>20.34591921171301</v>
+        <v>35.91872834392029</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P15">
-        <v>40.12642960440956</v>
+        <v>51.62987554632827</v>
       </c>
       <c r="Q15">
-        <v>56.79665501365471</v>
+        <v>74.37264188394303</v>
       </c>
       <c r="R15">
-        <v>65.21221375623318</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="S15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T15" t="b">
         <v>1</v>
@@ -1645,28 +1633,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
         <v>74</v>
       </c>
       <c r="G16">
-        <v>59.08407992144435</v>
+        <v>34.68945945985256</v>
       </c>
       <c r="H16">
-        <v>85.33233388124617</v>
+        <v>55.50706608529354</v>
       </c>
       <c r="I16">
-        <v>98.4319211743813</v>
+        <v>66.93645048851229</v>
       </c>
       <c r="J16">
         <v>120</v>
@@ -1675,28 +1663,28 @@
         <v>1</v>
       </c>
       <c r="L16">
-        <v>5.440500810633867</v>
+        <v>2.546881484042609</v>
       </c>
       <c r="M16">
-        <v>0.3199373986707666</v>
+        <v>0.3632796289893477</v>
       </c>
       <c r="N16">
-        <v>38.44670504800009</v>
+        <v>29.50525516252995</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P16">
-        <v>36.44969671862485</v>
+        <v>26.08578415182364</v>
       </c>
       <c r="Q16">
-        <v>62.69795067842667</v>
+        <v>46.90339077726461</v>
       </c>
       <c r="R16">
-        <v>75.79753797156181</v>
+        <v>58.33277518048336</v>
       </c>
       <c r="S16" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T16" t="b">
         <v>1</v>
@@ -1707,28 +1695,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>75</v>
       </c>
       <c r="G17">
-        <v>69.29126159516773</v>
+        <v>58.49510039853959</v>
       </c>
       <c r="H17">
-        <v>85.7895130065356</v>
+        <v>79.31270702398058</v>
       </c>
       <c r="I17">
-        <v>91.08159775123681</v>
+        <v>90.74209142719931</v>
       </c>
       <c r="J17">
         <v>120</v>
@@ -1737,28 +1725,28 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>1.914498008428869</v>
+        <v>2.240674227365981</v>
       </c>
       <c r="M17">
-        <v>0.7606877489463914</v>
+        <v>0.4398314431585046</v>
       </c>
       <c r="N17">
-        <v>22.53072017693587</v>
+        <v>27.29375830875431</v>
       </c>
       <c r="O17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P17">
-        <v>59.08407992144435</v>
+        <v>49.86956876012783</v>
       </c>
       <c r="Q17">
-        <v>75.58233133281222</v>
+        <v>70.68717538556881</v>
       </c>
       <c r="R17">
-        <v>80.87441607751343</v>
+        <v>82.11655978878755</v>
       </c>
       <c r="S17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T17" t="b">
         <v>1</v>
@@ -1769,28 +1757,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
         <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>76</v>
       </c>
       <c r="G18">
-        <v>46.39412682011481</v>
+        <v>42.66090617600025</v>
       </c>
       <c r="H18">
-        <v>67.21173344555578</v>
+        <v>57.88474614762662</v>
       </c>
       <c r="I18">
-        <v>78.64111784877454</v>
+        <v>63.67114167480854</v>
       </c>
       <c r="J18">
         <v>120</v>
@@ -1799,28 +1787,28 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <v>2.546881484042609</v>
+        <v>1.048835444247772</v>
       </c>
       <c r="M18">
-        <v>0.3632796289893477</v>
+        <v>0.7669254568338284</v>
       </c>
       <c r="N18">
-        <v>29.50525516252995</v>
+        <v>13.38328176860038</v>
       </c>
       <c r="O18">
         <v>2</v>
       </c>
       <c r="P18">
-        <v>46.39412682011481</v>
+        <v>35.49285073617485</v>
       </c>
       <c r="Q18">
-        <v>67.21173344555578</v>
+        <v>50.71669070780122</v>
       </c>
       <c r="R18">
-        <v>78.64111784877454</v>
+        <v>56.50308623498314</v>
       </c>
       <c r="S18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T18" t="b">
         <v>1</v>
@@ -1831,28 +1819,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
         <v>77</v>
       </c>
       <c r="G19">
-        <v>65.21221375623318</v>
+        <v>52.95298043582615</v>
       </c>
       <c r="H19">
-        <v>86.02982038167417</v>
+        <v>74.37130194690481</v>
       </c>
       <c r="I19">
-        <v>97.4592047848929</v>
+        <v>86.39162345798346</v>
       </c>
       <c r="J19">
         <v>120</v>
@@ -1861,28 +1849,28 @@
         <v>1</v>
       </c>
       <c r="L19">
-        <v>2.240674227365981</v>
+        <v>2.409990591769786</v>
       </c>
       <c r="M19">
-        <v>0.4398314431585046</v>
+        <v>0.4644465351622699</v>
       </c>
       <c r="N19">
-        <v>27.29375830875431</v>
+        <v>19.93699173815082</v>
       </c>
       <c r="O19">
         <v>2</v>
       </c>
       <c r="P19">
-        <v>65.21221375623318</v>
+        <v>43.04730558427778</v>
       </c>
       <c r="Q19">
-        <v>86.02982038167417</v>
+        <v>64.46562709535644</v>
       </c>
       <c r="R19">
-        <v>97.4592047848929</v>
+        <v>76.48594860643509</v>
       </c>
       <c r="S19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T19" t="b">
         <v>1</v>
@@ -1896,25 +1884,25 @@
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
         <v>78</v>
       </c>
       <c r="G20">
-        <v>42.34431787370568</v>
+        <v>56.25431253974453</v>
       </c>
       <c r="H20">
-        <v>65.10697432608441</v>
+        <v>76.19365451958166</v>
       </c>
       <c r="I20">
-        <v>78.52874188957426</v>
+        <v>88.0183298327521</v>
       </c>
       <c r="J20">
         <v>120</v>
@@ -1923,28 +1911,28 @@
         <v>1</v>
       </c>
       <c r="L20">
-        <v>2.660432042052936</v>
+        <v>1.976874086653691</v>
       </c>
       <c r="M20">
-        <v>0.408792879543792</v>
+        <v>0.5606946474102907</v>
       </c>
       <c r="N20">
-        <v>21.14282094321784</v>
+        <v>17.85161597277703</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P20">
-        <v>52.95298043582615</v>
+        <v>51.02181828239844</v>
       </c>
       <c r="Q20">
-        <v>75.71563688820488</v>
+        <v>70.96116026223557</v>
       </c>
       <c r="R20">
-        <v>89.13740445169474</v>
+        <v>82.78583557540601</v>
       </c>
       <c r="S20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T20" t="b">
         <v>1</v>
@@ -1955,28 +1943,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>79</v>
       </c>
       <c r="G21">
-        <v>52.95298043582615</v>
+        <v>60.92749313394681</v>
       </c>
       <c r="H21">
-        <v>74.37130194690481</v>
+        <v>75.15133310557317</v>
       </c>
       <c r="I21">
-        <v>86.39162345798346</v>
+        <v>80.93772863275511</v>
       </c>
       <c r="J21">
         <v>120</v>
@@ -1985,28 +1973,28 @@
         <v>1</v>
       </c>
       <c r="L21">
-        <v>2.409990591769786</v>
+        <v>1.014245103020607</v>
       </c>
       <c r="M21">
-        <v>0.4644465351622699</v>
+        <v>0.7746121993287539</v>
       </c>
       <c r="N21">
-        <v>19.93699173815082</v>
+        <v>13.21673568121033</v>
       </c>
       <c r="O21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>60.92749313394681</v>
+        <v>55.37837351819476</v>
       </c>
       <c r="Q21">
-        <v>82.34581464502547</v>
+        <v>69.60221348982112</v>
       </c>
       <c r="R21">
-        <v>94.36613615610412</v>
+        <v>75.38860901700306</v>
       </c>
       <c r="S21" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T21" t="b">
         <v>1</v>
@@ -2020,25 +2008,25 @@
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
       </c>
       <c r="G22">
-        <v>62.17479007886146</v>
+        <v>65.28404836974312</v>
       </c>
       <c r="H22">
-        <v>83.9374465312402</v>
+        <v>79.84533046929874</v>
       </c>
       <c r="I22">
-        <v>97.35921409473004</v>
+        <v>86.11450145774324</v>
       </c>
       <c r="J22">
         <v>120</v>
@@ -2047,28 +2035,28 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <v>2.623902934018422</v>
+        <v>1.066023243410243</v>
       </c>
       <c r="M22">
-        <v>0.4169104591070174</v>
+        <v>0.7631059459088348</v>
       </c>
       <c r="N22">
-        <v>20.96694005268129</v>
+        <v>13.46603783864191</v>
       </c>
       <c r="O22">
         <v>1</v>
       </c>
       <c r="P22">
-        <v>69.17468048177344</v>
+        <v>56.50308623498314</v>
       </c>
       <c r="Q22">
-        <v>90.93733693415217</v>
+        <v>71.06436833453876</v>
       </c>
       <c r="R22">
-        <v>104.359104497642</v>
+        <v>77.33353932298327</v>
       </c>
       <c r="S22" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="T22" t="b">
         <v>1</v>
@@ -2079,28 +2067,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F23" t="s">
         <v>81</v>
       </c>
       <c r="G23">
-        <v>92.47697847418542</v>
+        <v>80.93772863275511</v>
       </c>
       <c r="H23">
-        <v>111.9916814491121</v>
+        <v>98.86734894077981</v>
       </c>
       <c r="I23">
-        <v>122.9843844240387</v>
+        <v>108.5423025821379</v>
       </c>
       <c r="J23">
         <v>120</v>
@@ -2109,28 +2097,28 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <v>3.56316577275202</v>
+        <v>1.571297495086422</v>
       </c>
       <c r="M23">
-        <v>0.5546042784059975</v>
+        <v>0.6508227788696839</v>
       </c>
       <c r="N23">
-        <v>29.97262327978342</v>
+        <v>15.89883979115685</v>
       </c>
       <c r="O23">
         <v>1</v>
       </c>
       <c r="P23">
-        <v>75.79753797156181</v>
+        <v>75.38860901700306</v>
       </c>
       <c r="Q23">
-        <v>95.31224094648847</v>
+        <v>93.31822932502776</v>
       </c>
       <c r="R23">
-        <v>106.3049439214151</v>
+        <v>102.9931829663858</v>
       </c>
       <c r="S23" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T23" t="b">
         <v>1</v>
@@ -2141,28 +2129,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
         <v>82</v>
       </c>
       <c r="G24">
-        <v>69.17468048177344</v>
+        <v>86.11450145774324</v>
       </c>
       <c r="H24">
-        <v>83.73596258132906</v>
+        <v>103.4593474567197</v>
       </c>
       <c r="I24">
-        <v>90.00513356977356</v>
+        <v>112.552971233474</v>
       </c>
       <c r="J24">
         <v>120</v>
@@ -2171,28 +2159,28 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <v>1.066023243410243</v>
+        <v>1.581530554767664</v>
       </c>
       <c r="M24">
-        <v>0.7631059459088348</v>
+        <v>0.6485487656071858</v>
       </c>
       <c r="N24">
-        <v>13.46603783864191</v>
+        <v>15.94811007851097</v>
       </c>
       <c r="O24">
         <v>1</v>
       </c>
       <c r="P24">
-        <v>74.78296089586298</v>
+        <v>76.48594860643509</v>
       </c>
       <c r="Q24">
-        <v>89.34424299541861</v>
+        <v>93.83079460541157</v>
       </c>
       <c r="R24">
-        <v>95.61341398386311</v>
+        <v>102.9244183821658</v>
       </c>
       <c r="S24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T24" t="b">
         <v>1</v>
@@ -2203,28 +2191,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F25" t="s">
         <v>83</v>
       </c>
       <c r="G25">
-        <v>78.52874188957426</v>
+        <v>66.93645048851229</v>
       </c>
       <c r="H25">
-        <v>96.45836219759896</v>
+        <v>86.11986242216884</v>
       </c>
       <c r="I25">
-        <v>106.133315838957</v>
+        <v>96.97227435582539</v>
       </c>
       <c r="J25">
         <v>120</v>
@@ -2233,28 +2221,28 @@
         <v>1</v>
       </c>
       <c r="L25">
-        <v>1.571297495086422</v>
+        <v>1.971677737898548</v>
       </c>
       <c r="M25">
-        <v>0.6508227788696839</v>
+        <v>0.5070805655253631</v>
       </c>
       <c r="N25">
-        <v>15.89883979115685</v>
+        <v>25.35100588482284</v>
       </c>
       <c r="O25">
         <v>1</v>
       </c>
       <c r="P25">
-        <v>89.13740445169474</v>
+        <v>58.33277518048336</v>
       </c>
       <c r="Q25">
-        <v>107.0670247597194</v>
+        <v>77.51618711413991</v>
       </c>
       <c r="R25">
-        <v>116.7419784010775</v>
+        <v>88.36859904779647</v>
       </c>
       <c r="S25" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T25" t="b">
         <v>1</v>
@@ -2268,25 +2256,25 @@
         <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
         <v>84</v>
       </c>
       <c r="G26">
-        <v>89.00515268692922</v>
+        <v>94.15446431396543</v>
       </c>
       <c r="H26">
-        <v>106.3499986859057</v>
+        <v>111.1952011735548</v>
       </c>
       <c r="I26">
-        <v>115.4436224626599</v>
+        <v>119.9848269220332</v>
       </c>
       <c r="J26">
         <v>120</v>
@@ -2295,28 +2283,28 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <v>1.581530554767664</v>
+        <v>1.575202255282084</v>
       </c>
       <c r="M26">
-        <v>0.6485487656071858</v>
+        <v>0.6499550543817592</v>
       </c>
       <c r="N26">
-        <v>15.94811007851097</v>
+        <v>15.91764048839522</v>
       </c>
       <c r="O26">
         <v>1</v>
       </c>
       <c r="P26">
-        <v>94.61343310101877</v>
+        <v>88.6053446982134</v>
       </c>
       <c r="Q26">
-        <v>111.9582790999953</v>
+        <v>105.6460815578028</v>
       </c>
       <c r="R26">
-        <v>121.0519028767495</v>
+        <v>114.4357073062812</v>
       </c>
       <c r="S26" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T26" t="b">
         <v>1</v>
@@ -2327,28 +2315,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F27" t="s">
         <v>85</v>
       </c>
       <c r="G27">
-        <v>78.64111784877454</v>
+        <v>90.74209142719931</v>
       </c>
       <c r="H27">
-        <v>97.8245297824311</v>
+        <v>109.4557330066351</v>
       </c>
       <c r="I27">
-        <v>108.6769417160876</v>
+        <v>119.9174856971819</v>
       </c>
       <c r="J27">
         <v>120</v>
@@ -2357,28 +2345,28 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <v>1.971677737898548</v>
+        <v>1.607789512414177</v>
       </c>
       <c r="M27">
-        <v>0.5070805655253631</v>
+        <v>0.5980526218964557</v>
       </c>
       <c r="N27">
-        <v>25.35100588482284</v>
+        <v>22.72292425632461</v>
       </c>
       <c r="O27">
         <v>1</v>
       </c>
       <c r="P27">
-        <v>78.64111784877454</v>
+        <v>82.11655978878755</v>
       </c>
       <c r="Q27">
-        <v>97.8245297824311</v>
+        <v>100.8302013682233</v>
       </c>
       <c r="R27">
-        <v>108.6769417160876</v>
+        <v>111.2919540587701</v>
       </c>
       <c r="S27" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T27" t="b">
         <v>1</v>
@@ -2389,58 +2377,58 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s">
         <v>86</v>
       </c>
       <c r="G28">
-        <v>97.4592047848929</v>
+        <v>83.30807275110952</v>
       </c>
       <c r="H28">
-        <v>113.1530804493157</v>
+        <v>103.944024092142</v>
       </c>
       <c r="I28">
-        <v>120.5958450026275</v>
+        <v>112.2921420998412</v>
       </c>
       <c r="J28">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28">
-        <v>1.309771480726076</v>
+        <v>3.517681856451785</v>
       </c>
       <c r="M28">
-        <v>0.672557129818481</v>
+        <v>0.5602897679435269</v>
       </c>
       <c r="N28">
-        <v>20.57057180524388</v>
+        <v>29.76731393537263</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>97.4592047848929</v>
+        <v>73.40239789956115</v>
       </c>
       <c r="Q28">
-        <v>113.1530804493157</v>
+        <v>94.03834924059366</v>
       </c>
       <c r="R28">
-        <v>120.5958450026275</v>
+        <v>102.3864672482928</v>
       </c>
       <c r="S28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T28" t="b">
         <v>1</v>
@@ -2451,58 +2439,58 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s">
         <v>87</v>
       </c>
       <c r="G29">
-        <v>99.37874741911503</v>
+        <v>99.58053929638515</v>
       </c>
       <c r="H29">
-        <v>119.6134465240531</v>
+        <v>118.3453744515041</v>
       </c>
       <c r="I29">
-        <v>131.1203122956579</v>
+        <v>127.7238762732897</v>
       </c>
       <c r="J29">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29">
-        <v>3.492318945036377</v>
+        <v>1.8710546231918</v>
       </c>
       <c r="M29">
-        <v>0.5634601318704529</v>
+        <v>0.5842100837351556</v>
       </c>
       <c r="N29">
-        <v>29.65282857134476</v>
+        <v>17.34211485240496</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29">
-        <v>92.47697847418542</v>
+        <v>90.79957716162518</v>
       </c>
       <c r="Q29">
-        <v>112.7116775791235</v>
+        <v>109.5644123167441</v>
       </c>
       <c r="R29">
-        <v>124.2185433507283</v>
+        <v>118.9429141385297</v>
       </c>
       <c r="S29" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T29" t="b">
         <v>1</v>
@@ -2516,25 +2504,25 @@
         <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
         <v>88</v>
       </c>
       <c r="G30">
-        <v>99.67156283279211</v>
+        <v>108.5423025821379</v>
       </c>
       <c r="H30">
-        <v>118.4543771143929</v>
+        <v>123.3749793107571</v>
       </c>
       <c r="I30">
-        <v>127.8119691737715</v>
+        <v>128.801433817154</v>
       </c>
       <c r="J30">
         <v>180</v>
@@ -2543,28 +2531,28 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>1.779919328040352</v>
+        <v>0.974739867166567</v>
       </c>
       <c r="M30">
-        <v>0.6044623715465884</v>
+        <v>0.7833911406296518</v>
       </c>
       <c r="N30">
-        <v>16.90331528315725</v>
+        <v>13.02652528635754</v>
       </c>
       <c r="O30">
         <v>2</v>
       </c>
       <c r="P30">
-        <v>109.079451822505</v>
+        <v>102.9244183821658</v>
       </c>
       <c r="Q30">
-        <v>127.8622661041058</v>
+        <v>117.757095110785</v>
       </c>
       <c r="R30">
-        <v>137.2198581634844</v>
+        <v>123.1835496171819</v>
       </c>
       <c r="S30" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="T30" t="b">
         <v>1</v>
@@ -2575,28 +2563,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
         <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>89</v>
       </c>
       <c r="G31">
-        <v>103.4711714084155</v>
+        <v>96.97227435582539</v>
       </c>
       <c r="H31">
-        <v>122.2360065635344</v>
+        <v>111.3451679121932</v>
       </c>
       <c r="I31">
-        <v>131.61450838532</v>
+        <v>116.2806170241165</v>
       </c>
       <c r="J31">
         <v>180</v>
@@ -2605,28 +2593,28 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>1.8710546231918</v>
+        <v>0.8736555559417358</v>
       </c>
       <c r="M31">
-        <v>0.5842100837351556</v>
+        <v>0.7815861110145661</v>
       </c>
       <c r="N31">
-        <v>17.34211485240496</v>
+        <v>17.42084568180142</v>
       </c>
       <c r="O31">
         <v>2</v>
       </c>
       <c r="P31">
-        <v>110.2802253949126</v>
+        <v>88.36859904779647</v>
       </c>
       <c r="Q31">
-        <v>129.0450605500315</v>
+        <v>102.7414926041643</v>
       </c>
       <c r="R31">
-        <v>138.4235623718171</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="S31" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T31" t="b">
         <v>1</v>
@@ -2637,28 +2625,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
         <v>90</v>
       </c>
       <c r="G32">
-        <v>108.6769417160876</v>
+        <v>118.0358497359536</v>
       </c>
       <c r="H32">
-        <v>122.7270773797231</v>
+        <v>139.4433870243834</v>
       </c>
       <c r="I32">
-        <v>127.3709908211363</v>
+        <v>151.5851465350355</v>
       </c>
       <c r="J32">
         <v>180</v>
@@ -2667,28 +2655,28 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>0.845945507122666</v>
+        <v>2.171939602406073</v>
       </c>
       <c r="M32">
-        <v>0.7885136232193335</v>
+        <v>0.4570150993984818</v>
       </c>
       <c r="N32">
-        <v>17.22071755144147</v>
+        <v>26.79734157293274</v>
       </c>
       <c r="O32">
         <v>2</v>
       </c>
       <c r="P32">
-        <v>108.6769417160876</v>
+        <v>109.4103180975419</v>
       </c>
       <c r="Q32">
-        <v>122.7270773797231</v>
+        <v>130.8178553859717</v>
       </c>
       <c r="R32">
-        <v>127.3709908211363</v>
+        <v>142.9596148966238</v>
       </c>
       <c r="S32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T32" t="b">
         <v>1</v>
@@ -2699,28 +2687,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
         <v>37</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F33" t="s">
         <v>91</v>
       </c>
       <c r="G33">
-        <v>122.9843844240387</v>
+        <v>112.552971233474</v>
       </c>
       <c r="H33">
-        <v>138.3826358354066</v>
+        <v>132.9712927445526</v>
       </c>
       <c r="I33">
-        <v>143.6747205801078</v>
+        <v>144.9916142556312</v>
       </c>
       <c r="J33">
         <v>180</v>
@@ -2729,28 +2717,28 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>1.835475722612836</v>
+        <v>2.306810552860246</v>
       </c>
       <c r="M33">
-        <v>0.7705655346733955</v>
+        <v>0.4873754326977231</v>
       </c>
       <c r="N33">
-        <v>22.17402235901627</v>
+        <v>19.440198958216</v>
       </c>
       <c r="O33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P33">
-        <v>106.3049439214151</v>
+        <v>102.9931829663858</v>
       </c>
       <c r="Q33">
-        <v>121.703195332783</v>
+        <v>123.4115044774644</v>
       </c>
       <c r="R33">
-        <v>126.9952800774842</v>
+        <v>135.4318259885431</v>
       </c>
       <c r="S33" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T33" t="b">
         <v>1</v>
@@ -2761,28 +2749,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F34" t="s">
         <v>92</v>
       </c>
       <c r="G34">
-        <v>124.7529630936472</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="H34">
-        <v>146.1605003820771</v>
+        <v>107.0726497510757</v>
       </c>
       <c r="I34">
-        <v>158.3022598927292</v>
+        <v>119.1588912805937</v>
       </c>
       <c r="J34">
         <v>180</v>
@@ -2791,28 +2779,28 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>2.171939602406073</v>
+        <v>4.403269646749423</v>
       </c>
       <c r="M34">
-        <v>0.4570150993984818</v>
+        <v>0.4495912941563222</v>
       </c>
       <c r="N34">
-        <v>26.79734157293274</v>
+        <v>33.7647588221328</v>
       </c>
       <c r="O34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P34">
-        <v>124.7529630936472</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="Q34">
-        <v>146.1605003820771</v>
+        <v>107.0726497510757</v>
       </c>
       <c r="R34">
-        <v>158.3022598927292</v>
+        <v>119.1588912805937</v>
       </c>
       <c r="S34" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T34" t="b">
         <v>1</v>
@@ -2823,28 +2811,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F35" t="s">
         <v>93</v>
       </c>
       <c r="G35">
-        <v>106.3286151961343</v>
+        <v>124.4411423732947</v>
       </c>
       <c r="H35">
-        <v>124.111429477735</v>
+        <v>139.0024244728503</v>
       </c>
       <c r="I35">
-        <v>133.4690215371136</v>
+        <v>145.2715954612948</v>
       </c>
       <c r="J35">
         <v>180</v>
@@ -2853,28 +2841,28 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>1.756036387465134</v>
+        <v>1.057798217128584</v>
       </c>
       <c r="M35">
-        <v>0.6097696916744146</v>
+        <v>0.7649337295269814</v>
       </c>
       <c r="N35">
-        <v>16.78832334705435</v>
+        <v>13.42643586024874</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35">
-        <v>116.7419784010775</v>
+        <v>118.8725284606768</v>
       </c>
       <c r="Q35">
-        <v>134.5247926826782</v>
+        <v>133.4338105602324</v>
       </c>
       <c r="R35">
-        <v>143.8823847420568</v>
+        <v>139.7029815486769</v>
       </c>
       <c r="S35" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="T35" t="b">
         <v>1</v>
@@ -2885,28 +2873,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F36" t="s">
         <v>94</v>
       </c>
       <c r="G36">
-        <v>118.3261541474113</v>
+        <v>121.7547777991096</v>
       </c>
       <c r="H36">
-        <v>136.1089684290122</v>
+        <v>139.7035136206564</v>
       </c>
       <c r="I36">
-        <v>145.4665604883906</v>
+        <v>148.9202494422031</v>
       </c>
       <c r="J36">
         <v>180</v>
@@ -2915,28 +2903,28 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>1.756036387465134</v>
+        <v>2.845453629675534</v>
       </c>
       <c r="M36">
-        <v>0.6097696916744146</v>
+        <v>0.6443182962905583</v>
       </c>
       <c r="N36">
-        <v>16.78832334705435</v>
+        <v>26.73295041172984</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36">
-        <v>125.3260445503233</v>
+        <v>111.8491029475612</v>
       </c>
       <c r="Q36">
-        <v>143.1088588319241</v>
+        <v>129.797838769108</v>
       </c>
       <c r="R36">
-        <v>152.4664508913026</v>
+        <v>139.0145745906547</v>
       </c>
       <c r="S36" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T36" t="b">
         <v>1</v>
@@ -2947,28 +2935,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
         <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E37" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F37" t="s">
         <v>95</v>
       </c>
       <c r="G37">
-        <v>127.8119691737715</v>
+        <v>122.3232802406482</v>
       </c>
       <c r="H37">
-        <v>148.2302906848501</v>
+        <v>141.8333083642319</v>
       </c>
       <c r="I37">
-        <v>160.2506121959288</v>
+        <v>153.0024475989267</v>
       </c>
       <c r="J37">
         <v>180</v>
@@ -2977,28 +2965,28 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>2.306810552860246</v>
+        <v>2.113150583946663</v>
       </c>
       <c r="M37">
-        <v>0.4873754326977231</v>
+        <v>0.4717123540133343</v>
       </c>
       <c r="N37">
-        <v>19.440198958216</v>
+        <v>26.37275421739256</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37">
-        <v>137.2198581634844</v>
+        <v>113.7196049326193</v>
       </c>
       <c r="Q37">
-        <v>157.638179674563</v>
+        <v>133.229633056203</v>
       </c>
       <c r="R37">
-        <v>169.6585011856417</v>
+        <v>144.3987722908978</v>
       </c>
       <c r="S37" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T37" t="b">
         <v>1</v>
@@ -3009,28 +2997,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F38" t="s">
         <v>96</v>
       </c>
       <c r="G38">
-        <v>131.61450838532</v>
+        <v>121.9728032321447</v>
       </c>
       <c r="H38">
-        <v>153.5836849393032</v>
+        <v>141.4875062070714</v>
       </c>
       <c r="I38">
-        <v>167.1646392710641</v>
+        <v>152.480209181998</v>
       </c>
       <c r="J38">
         <v>180</v>
@@ -3039,28 +3027,28 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <v>2.494804901151978</v>
+        <v>3.686771208193226</v>
       </c>
       <c r="M38">
-        <v>0.445598910855116</v>
+        <v>0.5391535989758467</v>
       </c>
       <c r="N38">
-        <v>20.34535693147248</v>
+        <v>30.53056448142775</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
       <c r="P38">
-        <v>138.4235623718171</v>
+        <v>121.9728032321447</v>
       </c>
       <c r="Q38">
-        <v>160.3927389258003</v>
+        <v>141.4875062070714</v>
       </c>
       <c r="R38">
-        <v>173.9736932575612</v>
+        <v>152.480209181998</v>
       </c>
       <c r="S38" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T38" t="b">
         <v>1</v>
@@ -3074,55 +3062,55 @@
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F39" t="s">
         <v>97</v>
       </c>
       <c r="G39">
-        <v>144.7152844569287</v>
+        <v>128.5010813119849</v>
       </c>
       <c r="H39">
-        <v>159.2765665564843</v>
+        <v>150.9255812506797</v>
       </c>
       <c r="I39">
-        <v>165.5457375449288</v>
+        <v>165.0843034115967</v>
       </c>
       <c r="J39">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>1.057798217128584</v>
+        <v>2.412427120788479</v>
       </c>
       <c r="M39">
-        <v>0.7649337295269814</v>
+        <v>0.4639050842692268</v>
       </c>
       <c r="N39">
-        <v>13.42643586024874</v>
+        <v>19.94872317416675</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39">
-        <v>154.1231734466416</v>
+        <v>118.9429141385297</v>
       </c>
       <c r="Q39">
-        <v>168.6844555461972</v>
+        <v>141.3674140772245</v>
       </c>
       <c r="R39">
-        <v>174.9536265346417</v>
+        <v>155.5261362381415</v>
       </c>
       <c r="S39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T39" t="b">
         <v>1</v>
@@ -3136,55 +3124,55 @@
         <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F40" t="s">
         <v>98</v>
       </c>
       <c r="G40">
-        <v>134.0279476009105</v>
+        <v>148.9202494422031</v>
       </c>
       <c r="H40">
-        <v>150.6981730101556</v>
+        <v>169.9388243050544</v>
       </c>
       <c r="I40">
-        <v>159.1137317527341</v>
+        <v>182.0250658345724</v>
       </c>
       <c r="J40">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>1.304041604369885</v>
+        <v>4.375001305345046</v>
       </c>
       <c r="M40">
-        <v>0.6739895989075286</v>
+        <v>0.4531248368318692</v>
       </c>
       <c r="N40">
-        <v>20.52918936489361</v>
+        <v>33.63715866996027</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40">
-        <v>134.0279476009105</v>
+        <v>139.0145745906547</v>
       </c>
       <c r="Q40">
-        <v>150.6981730101556</v>
+        <v>160.033149453506</v>
       </c>
       <c r="R40">
-        <v>159.1137317527341</v>
+        <v>172.119390983024</v>
       </c>
       <c r="S40" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T40" t="b">
         <v>1</v>
@@ -3195,58 +3183,58 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F41" t="s">
         <v>99</v>
       </c>
       <c r="G41">
-        <v>148.9566232377249</v>
+        <v>135.9024674104284</v>
       </c>
       <c r="H41">
-        <v>170.7192796901037</v>
+        <v>153.6852816920291</v>
       </c>
       <c r="I41">
-        <v>184.1410472535935</v>
+        <v>163.0428737514077</v>
       </c>
       <c r="J41">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>2.556464580723934</v>
+        <v>1.711944804864733</v>
       </c>
       <c r="M41">
-        <v>0.4318967598391258</v>
+        <v>0.6195678211411705</v>
       </c>
       <c r="N41">
-        <v>20.64223687015227</v>
+        <v>16.57603054194131</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41">
-        <v>155.765677224222</v>
+        <v>130.3533477946764</v>
       </c>
       <c r="Q41">
-        <v>177.5283336766009</v>
+        <v>148.1361620762771</v>
       </c>
       <c r="R41">
-        <v>190.9501012400906</v>
+        <v>157.4937541356557</v>
       </c>
       <c r="S41" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T41" t="b">
         <v>1</v>
@@ -3257,58 +3245,58 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F42" t="s">
         <v>100</v>
       </c>
       <c r="G42">
-        <v>136.8786262223814</v>
+        <v>151.5851465350355</v>
       </c>
       <c r="H42">
-        <v>156.3933291973081</v>
+        <v>171.0951746586192</v>
       </c>
       <c r="I42">
-        <v>167.3860321722347</v>
+        <v>182.2643138933139</v>
       </c>
       <c r="J42">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>3.686771208193226</v>
+        <v>2.080451140464154</v>
       </c>
       <c r="M42">
-        <v>0.5391535989758467</v>
+        <v>0.4798872148839615</v>
       </c>
       <c r="N42">
-        <v>30.53056448142775</v>
+        <v>26.13659157001889</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42">
-        <v>124.2185433507283</v>
+        <v>142.9596148966238</v>
       </c>
       <c r="Q42">
-        <v>143.733246325655</v>
+        <v>162.4696430202075</v>
       </c>
       <c r="R42">
-        <v>154.7259493005816</v>
+        <v>173.6387822549022</v>
       </c>
       <c r="S42" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T42" t="b">
         <v>1</v>
@@ -3319,28 +3307,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43">
-        <v>160.2506121959288</v>
+        <v>144.9916142556312</v>
       </c>
       <c r="H43">
-        <v>182.6751121346236</v>
+        <v>162.7564494107502</v>
       </c>
       <c r="I43">
-        <v>196.8338342955406</v>
+        <v>172.1349512325357</v>
       </c>
       <c r="J43">
         <v>240</v>
@@ -3349,28 +3337,28 @@
         <v>1</v>
       </c>
       <c r="L43">
-        <v>2.412427120788479</v>
+        <v>1.797687027182534</v>
       </c>
       <c r="M43">
-        <v>0.4639050842692268</v>
+        <v>0.6005139939594369</v>
       </c>
       <c r="N43">
-        <v>19.94872317416675</v>
+        <v>16.9888634642122</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43">
-        <v>169.6585011856417</v>
+        <v>136.2100749035394</v>
       </c>
       <c r="Q43">
-        <v>192.0830011243365</v>
+        <v>153.9749100586583</v>
       </c>
       <c r="R43">
-        <v>206.2417232852535</v>
+        <v>163.3534118804439</v>
       </c>
       <c r="S43" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T43" t="b">
         <v>1</v>
@@ -3381,28 +3369,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E44" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F44" t="s">
         <v>102</v>
       </c>
       <c r="G44">
-        <v>158.3022598927292</v>
+        <v>152.9236501027265</v>
       </c>
       <c r="H44">
-        <v>178.1198665181702</v>
+        <v>166.8837186611424</v>
       </c>
       <c r="I44">
-        <v>189.5492509213889</v>
+        <v>171.884453886225</v>
       </c>
       <c r="J44">
         <v>240</v>
@@ -3411,28 +3399,28 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>2.039725715171945</v>
+        <v>1.681614284379605</v>
       </c>
       <c r="M44">
-        <v>0.4900685712070139</v>
+        <v>0.7897982144525494</v>
       </c>
       <c r="N44">
-        <v>25.84246349846404</v>
+        <v>21.47950892254682</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44">
-        <v>158.3022598927292</v>
+        <v>152.9236501027265</v>
       </c>
       <c r="Q44">
-        <v>178.1198665181702</v>
+        <v>166.8837186611424</v>
       </c>
       <c r="R44">
-        <v>189.5492509213889</v>
+        <v>171.884453886225</v>
       </c>
       <c r="S44" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T44" t="b">
         <v>1</v>
@@ -3443,28 +3431,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F45" t="s">
         <v>103</v>
       </c>
       <c r="G45">
-        <v>159.1137317527341</v>
+        <v>153.0024475989267</v>
       </c>
       <c r="H45">
-        <v>175.4237646988632</v>
+        <v>171.2698157913762</v>
       </c>
       <c r="I45">
-        <v>183.30857542277</v>
+        <v>181.4225173171591</v>
       </c>
       <c r="J45">
         <v>240</v>
@@ -3473,28 +3461,28 @@
         <v>1</v>
       </c>
       <c r="L45">
-        <v>1.42178203198294</v>
+        <v>1.684852321935074</v>
       </c>
       <c r="M45">
-        <v>0.6445544920042652</v>
+        <v>0.5787869195162316</v>
       </c>
       <c r="N45">
-        <v>21.37953689765456</v>
+        <v>23.2794889917533</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45">
-        <v>159.1137317527341</v>
+        <v>144.3987722908978</v>
       </c>
       <c r="Q45">
-        <v>175.4237646988632</v>
+        <v>162.6661404833473</v>
       </c>
       <c r="R45">
-        <v>183.30857542277</v>
+        <v>172.8188420091302</v>
       </c>
       <c r="S45" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T45" t="b">
         <v>1</v>
@@ -3505,308 +3493,60 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
         <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F46" t="s">
         <v>104</v>
       </c>
       <c r="G46">
-        <v>183.30857542277</v>
+        <v>145.2715954612948</v>
       </c>
       <c r="H46">
-        <v>202.8186035463537</v>
+        <v>163.0544097428956</v>
       </c>
       <c r="I46">
-        <v>213.9877427810484</v>
+        <v>172.4120018022741</v>
       </c>
       <c r="J46">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>2.080451140464154</v>
+        <v>1.698235657333516</v>
       </c>
       <c r="M46">
-        <v>0.4798872148839615</v>
+        <v>0.6226142983703299</v>
       </c>
       <c r="N46">
-        <v>26.13659157001889</v>
+        <v>16.51002353530952</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46">
-        <v>183.30857542277</v>
+        <v>139.7029815486769</v>
       </c>
       <c r="Q46">
-        <v>202.8186035463537</v>
+        <v>157.4857958302777</v>
       </c>
       <c r="R46">
-        <v>213.9877427810484</v>
+        <v>166.8433878896562</v>
       </c>
       <c r="S46" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" t="s">
-        <v>58</v>
-      </c>
-      <c r="F47" t="s">
-        <v>105</v>
-      </c>
-      <c r="G47">
-        <v>152.9570077038221</v>
-      </c>
-      <c r="H47">
-        <v>170.0159568213422</v>
-      </c>
-      <c r="I47">
-        <v>178.1454059388622</v>
-      </c>
-      <c r="J47">
-        <v>240</v>
-      </c>
-      <c r="K47" t="b">
-        <v>1</v>
-      </c>
-      <c r="L47">
-        <v>3.136485864490634</v>
-      </c>
-      <c r="M47">
-        <v>0.6079392669386707</v>
-      </c>
-      <c r="N47">
-        <v>28.04663758277022</v>
-      </c>
-      <c r="O47">
-        <v>1</v>
-      </c>
-      <c r="P47">
-        <v>136.2775672011985</v>
-      </c>
-      <c r="Q47">
-        <v>153.3365163187186</v>
-      </c>
-      <c r="R47">
-        <v>161.4659654362386</v>
-      </c>
-      <c r="S47" t="s">
-        <v>110</v>
-      </c>
-      <c r="T47" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" t="s">
-        <v>40</v>
-      </c>
-      <c r="E48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" t="s">
-        <v>106</v>
-      </c>
-      <c r="G48">
-        <v>167.3860321722347</v>
-      </c>
-      <c r="H48">
-        <v>181.3461007306506</v>
-      </c>
-      <c r="I48">
-        <v>186.3468359557332</v>
-      </c>
-      <c r="J48">
-        <v>240</v>
-      </c>
-      <c r="K48" t="b">
-        <v>1</v>
-      </c>
-      <c r="L48">
-        <v>1.681614284379605</v>
-      </c>
-      <c r="M48">
-        <v>0.7897982144525494</v>
-      </c>
-      <c r="N48">
-        <v>21.47950892254682</v>
-      </c>
-      <c r="O48">
-        <v>1</v>
-      </c>
-      <c r="P48">
-        <v>154.7259493005816</v>
-      </c>
-      <c r="Q48">
-        <v>168.6860178589975</v>
-      </c>
-      <c r="R48">
-        <v>173.6867530840801</v>
-      </c>
-      <c r="S48" t="s">
-        <v>109</v>
-      </c>
-      <c r="T48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C49" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" t="s">
-        <v>41</v>
-      </c>
-      <c r="E49" t="s">
-        <v>56</v>
-      </c>
-      <c r="F49" t="s">
-        <v>107</v>
-      </c>
-      <c r="G49">
-        <v>165.5457375449288</v>
-      </c>
-      <c r="H49">
-        <v>185.4850795247659</v>
-      </c>
-      <c r="I49">
-        <v>197.3097548379364</v>
-      </c>
-      <c r="J49">
-        <v>240</v>
-      </c>
-      <c r="K49" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49">
-        <v>2.014825572369929</v>
-      </c>
-      <c r="M49">
-        <v>0.5522609839177937</v>
-      </c>
-      <c r="N49">
-        <v>18.0343453484478</v>
-      </c>
-      <c r="O49">
-        <v>1</v>
-      </c>
-      <c r="P49">
-        <v>173.9736932575612</v>
-      </c>
-      <c r="Q49">
-        <v>193.9130352373983</v>
-      </c>
-      <c r="R49">
-        <v>205.7377105505688</v>
-      </c>
-      <c r="S49" t="s">
-        <v>111</v>
-      </c>
-      <c r="T49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" t="s">
-        <v>57</v>
-      </c>
-      <c r="F50" t="s">
-        <v>108</v>
-      </c>
-      <c r="G50">
-        <v>178.9721734051776</v>
-      </c>
-      <c r="H50">
-        <v>196.7549876867784</v>
-      </c>
-      <c r="I50">
-        <v>206.1125797461569</v>
-      </c>
-      <c r="J50">
-        <v>300</v>
-      </c>
-      <c r="K50" t="b">
-        <v>1</v>
-      </c>
-      <c r="L50">
-        <v>1.698235657333516</v>
-      </c>
-      <c r="M50">
-        <v>0.6226142983703299</v>
-      </c>
-      <c r="N50">
-        <v>16.51002353530952</v>
-      </c>
-      <c r="O50">
-        <v>1</v>
-      </c>
-      <c r="P50">
-        <v>188.3800623948905</v>
-      </c>
-      <c r="Q50">
-        <v>206.1628766764913</v>
-      </c>
-      <c r="R50">
-        <v>215.5204687358698</v>
-      </c>
-      <c r="S50" t="s">
-        <v>111</v>
-      </c>
-      <c r="T50" t="b">
         <v>1</v>
       </c>
     </row>

--- a/结果/问题三_运输调度_修复版.xlsx
+++ b/结果/问题三_运输调度_修复版.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="107">
   <si>
     <t>mission_id</t>
   </si>
@@ -82,15 +82,15 @@
     <t>UC02</t>
   </si>
   <si>
+    <t>UB01</t>
+  </si>
+  <si>
+    <t>UB02</t>
+  </si>
+  <si>
     <t>UA01</t>
   </si>
   <si>
-    <t>UB01</t>
-  </si>
-  <si>
-    <t>UB02</t>
-  </si>
-  <si>
     <t>UA02</t>
   </si>
   <si>
@@ -103,12 +103,12 @@
     <t>C</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>C-BAT-01</t>
   </si>
   <si>
@@ -118,18 +118,21 @@
     <t>C-BAT-03</t>
   </si>
   <si>
+    <t>B-BAT-01</t>
+  </si>
+  <si>
+    <t>B-BAT-02</t>
+  </si>
+  <si>
     <t>A-BAT-01</t>
   </si>
   <si>
-    <t>B-BAT-01</t>
-  </si>
-  <si>
-    <t>B-BAT-02</t>
-  </si>
-  <si>
     <t>A-BAT-02</t>
   </si>
   <si>
+    <t>B-BAT-03</t>
+  </si>
+  <si>
     <t>A-BAT-03</t>
   </si>
   <si>
@@ -139,18 +142,15 @@
     <t>A-BAT-05</t>
   </si>
   <si>
+    <t>C-BAT-04</t>
+  </si>
+  <si>
+    <t>B-BAT-04</t>
+  </si>
+  <si>
     <t>A-BAT-06</t>
   </si>
   <si>
-    <t>B-BAT-03</t>
-  </si>
-  <si>
-    <t>C-BAT-04</t>
-  </si>
-  <si>
-    <t>B-BAT-04</t>
-  </si>
-  <si>
     <t>S001</t>
   </si>
   <si>
@@ -205,10 +205,13 @@
     <t>S001-WAT-06,S001-WAT-07,S001-WAT-08</t>
   </si>
   <si>
-    <t>S006-WAT-01,S006-MED-01</t>
-  </si>
-  <si>
-    <t>S007-WAT-01,S007-WAT-02</t>
+    <t>S006-WAT-01,S006-WAT-02</t>
+  </si>
+  <si>
+    <t>S006-WAT-03,S006-MED-01</t>
+  </si>
+  <si>
+    <t>S007-WAT-01,S007-MED-01</t>
   </si>
   <si>
     <t>S010-WAT-01,S010-MED-01</t>
@@ -223,13 +226,7 @@
     <t>S014-WAT-01,S014-MED-01</t>
   </si>
   <si>
-    <t>S006-WAT-02</t>
-  </si>
-  <si>
-    <t>S006-WAT-03</t>
-  </si>
-  <si>
-    <t>S007-MED-01</t>
+    <t>S007-WAT-02</t>
   </si>
   <si>
     <t>S003-WAT-01,S003-WAT-02,S003-WAT-03,S003-WAT-04,S003-MED-01</t>
@@ -695,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -816,7 +813,7 @@
         <v>26.19033615606908</v>
       </c>
       <c r="S2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -878,7 +875,7 @@
         <v>34.05455664662419</v>
       </c>
       <c r="S3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -940,7 +937,7 @@
         <v>47.98067231213816</v>
       </c>
       <c r="S4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T4" t="b">
         <v>1</v>
@@ -969,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>15.56128209955562</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="I5">
-        <v>21.83045308800013</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="J5">
         <v>60</v>
@@ -981,13 +978,13 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1.106805665390136</v>
+        <v>1.087081446911481</v>
       </c>
       <c r="M5">
-        <v>0.7540431854688587</v>
+        <v>0.7282296382721298</v>
       </c>
       <c r="N5">
-        <v>13.66239764817473</v>
+        <v>18.96225489436069</v>
       </c>
       <c r="O5">
         <v>2</v>
@@ -996,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>15.56128209955562</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="R5">
-        <v>21.83045308800013</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="S5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -1016,25 +1013,25 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
       </c>
       <c r="G6">
-        <v>7.323532094892318</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>24.99375750413748</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="I6">
-        <v>33.40931624671596</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -1043,13 +1040,13 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>1.60089897336792</v>
+        <v>0.9613264853346692</v>
       </c>
       <c r="M6">
-        <v>0.5997752566580201</v>
+        <v>0.7596683786663327</v>
       </c>
       <c r="N6">
-        <v>22.67315925210164</v>
+        <v>18.05402461630594</v>
       </c>
       <c r="O6">
         <v>2</v>
@@ -1058,13 +1055,13 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>17.67022540924516</v>
+        <v>14.67766295665795</v>
       </c>
       <c r="R6">
-        <v>26.08578415182364</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="S6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T6" t="b">
         <v>1</v>
@@ -1084,19 +1081,19 @@
         <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
       </c>
       <c r="G7">
-        <v>9.905674851548365</v>
+        <v>7.323532094892318</v>
       </c>
       <c r="H7">
-        <v>26.92317826681158</v>
+        <v>26.25315240291701</v>
       </c>
       <c r="I7">
-        <v>34.68945945985256</v>
+        <v>35.92810604427503</v>
       </c>
       <c r="J7">
         <v>60</v>
@@ -1105,13 +1102,13 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1.424415898434041</v>
+        <v>1.629423413491632</v>
       </c>
       <c r="M7">
-        <v>0.6438960253914898</v>
+        <v>0.6379059081129708</v>
       </c>
       <c r="N7">
-        <v>21.39855926646807</v>
+        <v>16.17870532421897</v>
       </c>
       <c r="O7">
         <v>2</v>
@@ -1120,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>17.01750341526321</v>
+        <v>18.92962030802469</v>
       </c>
       <c r="R7">
-        <v>24.7837846083042</v>
+        <v>28.60457394938271</v>
       </c>
       <c r="S7" t="s">
         <v>106</v>
@@ -1140,13 +1137,13 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
         <v>66</v>
@@ -1155,10 +1152,10 @@
         <v>9.905674851548365</v>
       </c>
       <c r="H8">
-        <v>27.9464117111378</v>
+        <v>28.25052085052485</v>
       </c>
       <c r="I8">
-        <v>36.73603745961613</v>
+        <v>37.34414462727911</v>
       </c>
       <c r="J8">
         <v>60</v>
@@ -1167,13 +1164,13 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1.637365079674389</v>
+        <v>1.642792520169815</v>
       </c>
       <c r="M8">
-        <v>0.6361410934056912</v>
+        <v>0.6349349955178188</v>
       </c>
       <c r="N8">
-        <v>16.21694297621002</v>
+        <v>16.24307509711392</v>
       </c>
       <c r="O8">
         <v>2</v>
@@ -1182,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>18.04073685958943</v>
+        <v>18.34484599897648</v>
       </c>
       <c r="R8">
-        <v>26.83036260806776</v>
+        <v>27.43846977573074</v>
       </c>
       <c r="S8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -1199,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
@@ -1208,19 +1205,19 @@
         <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>67</v>
       </c>
       <c r="G9">
-        <v>9.905674851548365</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="H9">
-        <v>32.14420882468487</v>
+        <v>36.75709046662761</v>
       </c>
       <c r="I9">
-        <v>45.05174279782136</v>
+        <v>44.19985501993932</v>
       </c>
       <c r="J9">
         <v>60</v>
@@ -1229,28 +1226,28 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>2.471325003399136</v>
+        <v>1.416012022961981</v>
       </c>
       <c r="M9">
-        <v>0.4508166659113031</v>
+        <v>0.6459969942595047</v>
       </c>
       <c r="N9">
-        <v>20.23230557192176</v>
+        <v>21.33786461028097</v>
       </c>
       <c r="O9">
         <v>2</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="Q9">
-        <v>22.2385339731365</v>
+        <v>36.75709046662761</v>
       </c>
       <c r="R9">
-        <v>35.146067946273</v>
+        <v>44.19985501993932</v>
       </c>
       <c r="S9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -1261,16 +1258,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
         <v>68</v>
@@ -1279,10 +1276,10 @@
         <v>9.905674851548365</v>
       </c>
       <c r="H10">
-        <v>31.12234688112371</v>
+        <v>32.14420882468487</v>
       </c>
       <c r="I10">
-        <v>43.0871300218102</v>
+        <v>45.05174279782136</v>
       </c>
       <c r="J10">
         <v>60</v>
@@ -1291,13 +1288,13 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>1.974536954059142</v>
+        <v>2.471325003399136</v>
       </c>
       <c r="M10">
-        <v>0.5612140102090795</v>
+        <v>0.4508166659113031</v>
       </c>
       <c r="N10">
-        <v>17.84036311213661</v>
+        <v>20.23230557192176</v>
       </c>
       <c r="O10">
         <v>2</v>
@@ -1306,13 +1303,13 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>21.21667202957535</v>
+        <v>22.2385339731365</v>
       </c>
       <c r="R10">
-        <v>33.18145517026183</v>
+        <v>35.146067946273</v>
       </c>
       <c r="S10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T10" t="b">
         <v>1</v>
@@ -1323,28 +1320,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
         <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
         <v>69</v>
       </c>
       <c r="G11">
-        <v>21.83045308800013</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H11">
-        <v>36.39173518755575</v>
+        <v>31.12234688112371</v>
       </c>
       <c r="I11">
-        <v>42.66090617600025</v>
+        <v>43.0871300218102</v>
       </c>
       <c r="J11">
         <v>60</v>
@@ -1353,25 +1350,25 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>1.092476706316119</v>
+        <v>1.974536954059142</v>
       </c>
       <c r="M11">
-        <v>0.757227398596418</v>
+        <v>0.5612140102090795</v>
       </c>
       <c r="N11">
-        <v>13.59340636374428</v>
+        <v>17.84036311213661</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11">
-        <v>21.83045308800013</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>36.39173518755575</v>
+        <v>21.21667202957535</v>
       </c>
       <c r="R11">
-        <v>42.66090617600025</v>
+        <v>33.18145517026183</v>
       </c>
       <c r="S11" t="s">
         <v>105</v>
@@ -1385,28 +1382,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
         <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
         <v>70</v>
       </c>
       <c r="G12">
-        <v>36.73603745961613</v>
+        <v>35.92810604427503</v>
       </c>
       <c r="H12">
-        <v>51.29731955917176</v>
+        <v>53.85772635229972</v>
       </c>
       <c r="I12">
-        <v>57.56649054761626</v>
+        <v>63.53267999365775</v>
       </c>
       <c r="J12">
         <v>60</v>
@@ -1415,28 +1412,28 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <v>1.092476706316119</v>
+        <v>1.609000793511423</v>
       </c>
       <c r="M12">
-        <v>0.757227398596418</v>
+        <v>0.6424442681085727</v>
       </c>
       <c r="N12">
-        <v>13.59340636374428</v>
+        <v>16.08037419098092</v>
       </c>
       <c r="O12">
         <v>1</v>
       </c>
       <c r="P12">
-        <v>26.83036260806776</v>
+        <v>27.43846977573074</v>
       </c>
       <c r="Q12">
-        <v>41.39164470762339</v>
+        <v>45.36809008375543</v>
       </c>
       <c r="R12">
-        <v>47.66081569606789</v>
+        <v>55.04304372511346</v>
       </c>
       <c r="S12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T12" t="b">
         <v>1</v>
@@ -1447,58 +1444,58 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
         <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
         <v>71</v>
       </c>
       <c r="G13">
-        <v>33.40931624671596</v>
+        <v>43.96023149817256</v>
       </c>
       <c r="H13">
-        <v>50.07954165596111</v>
+        <v>70.20848545797438</v>
       </c>
       <c r="I13">
-        <v>58.49510039853959</v>
+        <v>83.30807275110952</v>
       </c>
       <c r="J13">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
       </c>
       <c r="L13">
-        <v>1.278665737006417</v>
+        <v>5.440500810633867</v>
       </c>
       <c r="M13">
-        <v>0.6803335657483958</v>
+        <v>0.3199373986707666</v>
       </c>
       <c r="N13">
-        <v>20.34591921171301</v>
+        <v>38.44670504800009</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>24.7837846083042</v>
+        <v>34.05455664662419</v>
       </c>
       <c r="Q13">
-        <v>41.45401001754935</v>
+        <v>60.30281060642601</v>
       </c>
       <c r="R13">
-        <v>49.86956876012783</v>
+        <v>73.40239789956115</v>
       </c>
       <c r="S13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T13" t="b">
         <v>1</v>
@@ -1509,28 +1506,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
         <v>72</v>
       </c>
       <c r="G14">
-        <v>43.96023149817256</v>
+        <v>51.62987554632826</v>
       </c>
       <c r="H14">
-        <v>70.20848545797438</v>
+        <v>74.37264188394303</v>
       </c>
       <c r="I14">
-        <v>83.30807275110952</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="J14">
         <v>120</v>
@@ -1539,28 +1536,28 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <v>5.440500810633867</v>
+        <v>4.880456740806956</v>
       </c>
       <c r="M14">
-        <v>0.3199373986707666</v>
+        <v>0.3899429073991305</v>
       </c>
       <c r="N14">
-        <v>38.44670504800009</v>
+        <v>35.91872834392029</v>
       </c>
       <c r="O14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>34.05455664662419</v>
+        <v>51.62987554632827</v>
       </c>
       <c r="Q14">
-        <v>60.30281060642601</v>
+        <v>74.37264188394303</v>
       </c>
       <c r="R14">
-        <v>73.40239789956115</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="S14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T14" t="b">
         <v>1</v>
@@ -1571,28 +1568,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
         <v>73</v>
       </c>
       <c r="G15">
-        <v>51.62987554632826</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="H15">
-        <v>74.37264188394303</v>
+        <v>40.88082142764576</v>
       </c>
       <c r="I15">
-        <v>86.05407488822445</v>
+        <v>52.3102058308645</v>
       </c>
       <c r="J15">
         <v>120</v>
@@ -1601,28 +1598,28 @@
         <v>1</v>
       </c>
       <c r="L15">
-        <v>4.880456740806956</v>
+        <v>2.546881484042609</v>
       </c>
       <c r="M15">
-        <v>0.3899429073991305</v>
+        <v>0.3632796289893477</v>
       </c>
       <c r="N15">
-        <v>35.91872834392029</v>
+        <v>29.50525516252995</v>
       </c>
       <c r="O15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P15">
-        <v>51.62987554632827</v>
+        <v>20.06321480220478</v>
       </c>
       <c r="Q15">
-        <v>74.37264188394303</v>
+        <v>40.88082142764576</v>
       </c>
       <c r="R15">
-        <v>86.05407488822445</v>
+        <v>52.3102058308645</v>
       </c>
       <c r="S15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T15" t="b">
         <v>1</v>
@@ -1633,13 +1630,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>55</v>
@@ -1648,13 +1645,13 @@
         <v>74</v>
       </c>
       <c r="G16">
-        <v>34.68945945985256</v>
+        <v>44.19985501993932</v>
       </c>
       <c r="H16">
-        <v>55.50706608529354</v>
+        <v>65.01746164538029</v>
       </c>
       <c r="I16">
-        <v>66.93645048851229</v>
+        <v>76.44684604859904</v>
       </c>
       <c r="J16">
         <v>120</v>
@@ -1663,28 +1660,28 @@
         <v>1</v>
       </c>
       <c r="L16">
-        <v>2.546881484042609</v>
+        <v>2.240674227365981</v>
       </c>
       <c r="M16">
-        <v>0.3632796289893477</v>
+        <v>0.4398314431585046</v>
       </c>
       <c r="N16">
-        <v>29.50525516252995</v>
+        <v>27.29375830875431</v>
       </c>
       <c r="O16">
         <v>2</v>
       </c>
       <c r="P16">
-        <v>26.08578415182364</v>
+        <v>44.19985501993932</v>
       </c>
       <c r="Q16">
-        <v>46.90339077726461</v>
+        <v>65.01746164538029</v>
       </c>
       <c r="R16">
-        <v>58.33277518048336</v>
+        <v>76.44684604859904</v>
       </c>
       <c r="S16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T16" t="b">
         <v>1</v>
@@ -1695,28 +1692,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
         <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F17" t="s">
         <v>75</v>
       </c>
       <c r="G17">
-        <v>58.49510039853959</v>
+        <v>37.34414462727911</v>
       </c>
       <c r="H17">
-        <v>79.31270702398058</v>
+        <v>52.56798459890548</v>
       </c>
       <c r="I17">
-        <v>90.74209142719931</v>
+        <v>58.35438012608741</v>
       </c>
       <c r="J17">
         <v>120</v>
@@ -1725,28 +1722,28 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>2.240674227365981</v>
+        <v>1.048835444247772</v>
       </c>
       <c r="M17">
-        <v>0.4398314431585046</v>
+        <v>0.7669254568338284</v>
       </c>
       <c r="N17">
-        <v>27.29375830875431</v>
+        <v>13.38328176860038</v>
       </c>
       <c r="O17">
         <v>2</v>
       </c>
       <c r="P17">
-        <v>49.86956876012783</v>
+        <v>28.60457394938271</v>
       </c>
       <c r="Q17">
-        <v>70.68717538556881</v>
+        <v>43.82841392100908</v>
       </c>
       <c r="R17">
-        <v>82.11655978878755</v>
+        <v>49.61480944819101</v>
       </c>
       <c r="S17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T17" t="b">
         <v>1</v>
@@ -1757,28 +1754,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" t="s">
         <v>76</v>
       </c>
       <c r="G18">
-        <v>42.66090617600025</v>
+        <v>52.10681136849399</v>
       </c>
       <c r="H18">
-        <v>57.88474614762662</v>
+        <v>73.52513287957265</v>
       </c>
       <c r="I18">
-        <v>63.67114167480854</v>
+        <v>85.5454543906513</v>
       </c>
       <c r="J18">
         <v>120</v>
@@ -1787,25 +1784,25 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <v>1.048835444247772</v>
+        <v>2.409990591769786</v>
       </c>
       <c r="M18">
-        <v>0.7669254568338284</v>
+        <v>0.4644465351622699</v>
       </c>
       <c r="N18">
-        <v>13.38328176860038</v>
+        <v>19.93699173815082</v>
       </c>
       <c r="O18">
         <v>2</v>
       </c>
       <c r="P18">
-        <v>35.49285073617485</v>
+        <v>43.68154487284467</v>
       </c>
       <c r="Q18">
-        <v>50.71669070780122</v>
+        <v>65.09986638392333</v>
       </c>
       <c r="R18">
-        <v>56.50308623498314</v>
+        <v>77.12018789500198</v>
       </c>
       <c r="S18" t="s">
         <v>105</v>
@@ -1819,28 +1816,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
         <v>77</v>
       </c>
       <c r="G19">
-        <v>52.95298043582615</v>
+        <v>52.3102058308645</v>
       </c>
       <c r="H19">
-        <v>74.37130194690481</v>
+        <v>70.57757402331404</v>
       </c>
       <c r="I19">
-        <v>86.39162345798346</v>
+        <v>80.73027554909692</v>
       </c>
       <c r="J19">
         <v>120</v>
@@ -1849,25 +1846,25 @@
         <v>1</v>
       </c>
       <c r="L19">
-        <v>2.409990591769786</v>
+        <v>1.626892710624575</v>
       </c>
       <c r="M19">
-        <v>0.4644465351622699</v>
+        <v>0.5932768223438563</v>
       </c>
       <c r="N19">
-        <v>19.93699173815082</v>
+        <v>22.86089179895526</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <v>43.04730558427778</v>
+        <v>52.3102058308645</v>
       </c>
       <c r="Q19">
-        <v>64.46562709535644</v>
+        <v>70.57757402331404</v>
       </c>
       <c r="R19">
-        <v>76.48594860643509</v>
+        <v>80.73027554909692</v>
       </c>
       <c r="S19" t="s">
         <v>106</v>
@@ -1884,25 +1881,25 @@
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F20" t="s">
         <v>78</v>
       </c>
       <c r="G20">
-        <v>56.25431253974453</v>
+        <v>53.58721972439302</v>
       </c>
       <c r="H20">
-        <v>76.19365451958166</v>
+        <v>67.81105969601938</v>
       </c>
       <c r="I20">
-        <v>88.0183298327521</v>
+        <v>73.59745522320131</v>
       </c>
       <c r="J20">
         <v>120</v>
@@ -1911,28 +1908,28 @@
         <v>1</v>
       </c>
       <c r="L20">
-        <v>1.976874086653691</v>
+        <v>1.014245103020607</v>
       </c>
       <c r="M20">
-        <v>0.5606946474102907</v>
+        <v>0.7746121993287539</v>
       </c>
       <c r="N20">
-        <v>17.85161597277703</v>
+        <v>13.21673568121033</v>
       </c>
       <c r="O20">
         <v>1</v>
       </c>
       <c r="P20">
-        <v>51.02181828239844</v>
+        <v>44.78327927360168</v>
       </c>
       <c r="Q20">
-        <v>70.96116026223557</v>
+        <v>59.00711924522805</v>
       </c>
       <c r="R20">
-        <v>82.78583557540601</v>
+        <v>64.79351477240996</v>
       </c>
       <c r="S20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T20" t="b">
         <v>1</v>
@@ -1946,13 +1943,13 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s">
         <v>79</v>
@@ -1961,10 +1958,10 @@
         <v>60.92749313394681</v>
       </c>
       <c r="H21">
-        <v>75.15133310557317</v>
+        <v>75.48877523350244</v>
       </c>
       <c r="I21">
-        <v>80.93772863275511</v>
+        <v>81.75794622194694</v>
       </c>
       <c r="J21">
         <v>120</v>
@@ -1973,28 +1970,28 @@
         <v>1</v>
       </c>
       <c r="L21">
-        <v>1.014245103020607</v>
+        <v>1.066023243410243</v>
       </c>
       <c r="M21">
-        <v>0.7746121993287539</v>
+        <v>0.7631059459088348</v>
       </c>
       <c r="N21">
-        <v>13.21673568121033</v>
+        <v>13.46603783864191</v>
       </c>
       <c r="O21">
         <v>1</v>
       </c>
       <c r="P21">
-        <v>55.37837351819476</v>
+        <v>51.02181828239844</v>
       </c>
       <c r="Q21">
-        <v>69.60221348982112</v>
+        <v>65.58310038195407</v>
       </c>
       <c r="R21">
-        <v>75.38860901700306</v>
+        <v>71.85227137039857</v>
       </c>
       <c r="S21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T21" t="b">
         <v>1</v>
@@ -2005,16 +2002,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
@@ -2023,10 +2020,10 @@
         <v>65.28404836974312</v>
       </c>
       <c r="H22">
-        <v>79.84533046929874</v>
+        <v>83.21366867776781</v>
       </c>
       <c r="I22">
-        <v>86.11450145774324</v>
+        <v>92.88862231912583</v>
       </c>
       <c r="J22">
         <v>120</v>
@@ -2035,28 +2032,28 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <v>1.066023243410243</v>
+        <v>1.571297495086422</v>
       </c>
       <c r="M22">
-        <v>0.7631059459088348</v>
+        <v>0.6508227788696839</v>
       </c>
       <c r="N22">
-        <v>13.46603783864191</v>
+        <v>15.89883979115685</v>
       </c>
       <c r="O22">
         <v>1</v>
       </c>
       <c r="P22">
-        <v>56.50308623498314</v>
+        <v>55.37837351819476</v>
       </c>
       <c r="Q22">
-        <v>71.06436833453876</v>
+        <v>73.30799382621946</v>
       </c>
       <c r="R22">
-        <v>77.33353932298327</v>
+        <v>82.98294746757747</v>
       </c>
       <c r="S22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T22" t="b">
         <v>1</v>
@@ -2067,28 +2064,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s">
         <v>81</v>
       </c>
       <c r="G23">
-        <v>80.93772863275511</v>
+        <v>73.59745522320131</v>
       </c>
       <c r="H23">
-        <v>98.86734894077981</v>
+        <v>90.94230122217779</v>
       </c>
       <c r="I23">
-        <v>108.5423025821379</v>
+        <v>100.035924998932</v>
       </c>
       <c r="J23">
         <v>120</v>
@@ -2097,28 +2094,28 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <v>1.571297495086422</v>
+        <v>1.581530554767664</v>
       </c>
       <c r="M23">
-        <v>0.6508227788696839</v>
+        <v>0.6485487656071858</v>
       </c>
       <c r="N23">
-        <v>15.89883979115685</v>
+        <v>15.94811007851097</v>
       </c>
       <c r="O23">
         <v>1</v>
       </c>
       <c r="P23">
-        <v>75.38860901700306</v>
+        <v>64.79351477240996</v>
       </c>
       <c r="Q23">
-        <v>93.31822932502776</v>
+        <v>82.13836077138644</v>
       </c>
       <c r="R23">
-        <v>102.9931829663858</v>
+        <v>91.2319845481407</v>
       </c>
       <c r="S23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T23" t="b">
         <v>1</v>
@@ -2135,22 +2132,22 @@
         <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
         <v>82</v>
       </c>
       <c r="G24">
-        <v>86.11450145774324</v>
+        <v>76.44684604859904</v>
       </c>
       <c r="H24">
-        <v>103.4593474567197</v>
+        <v>95.6302579822556</v>
       </c>
       <c r="I24">
-        <v>112.552971233474</v>
+        <v>106.4826699159122</v>
       </c>
       <c r="J24">
         <v>120</v>
@@ -2159,28 +2156,28 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <v>1.581530554767664</v>
+        <v>1.971677737898548</v>
       </c>
       <c r="M24">
-        <v>0.6485487656071858</v>
+        <v>0.5070805655253631</v>
       </c>
       <c r="N24">
-        <v>15.94811007851097</v>
+        <v>25.35100588482284</v>
       </c>
       <c r="O24">
         <v>1</v>
       </c>
       <c r="P24">
-        <v>76.48594860643509</v>
+        <v>76.44684604859904</v>
       </c>
       <c r="Q24">
-        <v>93.83079460541157</v>
+        <v>95.6302579822556</v>
       </c>
       <c r="R24">
-        <v>102.9244183821658</v>
+        <v>106.4826699159122</v>
       </c>
       <c r="S24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T24" t="b">
         <v>1</v>
@@ -2191,28 +2188,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s">
         <v>83</v>
       </c>
       <c r="G25">
-        <v>66.93645048851229</v>
+        <v>81.81546099339445</v>
       </c>
       <c r="H25">
-        <v>86.11986242216884</v>
+        <v>97.50933665781729</v>
       </c>
       <c r="I25">
-        <v>96.97227435582539</v>
+        <v>104.952101211129</v>
       </c>
       <c r="J25">
         <v>120</v>
@@ -2221,28 +2218,28 @@
         <v>1</v>
       </c>
       <c r="L25">
-        <v>1.971677737898548</v>
+        <v>1.309771480726076</v>
       </c>
       <c r="M25">
-        <v>0.5070805655253631</v>
+        <v>0.672557129818481</v>
       </c>
       <c r="N25">
-        <v>25.35100588482284</v>
+        <v>20.57057180524388</v>
       </c>
       <c r="O25">
         <v>1</v>
       </c>
       <c r="P25">
-        <v>58.33277518048336</v>
+        <v>81.81546099339445</v>
       </c>
       <c r="Q25">
-        <v>77.51618711413991</v>
+        <v>97.50933665781729</v>
       </c>
       <c r="R25">
-        <v>88.36859904779647</v>
+        <v>104.952101211129</v>
       </c>
       <c r="S25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T25" t="b">
         <v>1</v>
@@ -2253,28 +2250,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F26" t="s">
         <v>84</v>
       </c>
       <c r="G26">
-        <v>94.15446431396543</v>
+        <v>81.75794622194694</v>
       </c>
       <c r="H26">
-        <v>111.1952011735548</v>
+        <v>101.9746182515223</v>
       </c>
       <c r="I26">
-        <v>119.9848269220332</v>
+        <v>113.9394013922088</v>
       </c>
       <c r="J26">
         <v>120</v>
@@ -2283,28 +2280,28 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <v>1.575202255282084</v>
+        <v>1.905166317898852</v>
       </c>
       <c r="M26">
-        <v>0.6499550543817592</v>
+        <v>0.5766297071335885</v>
       </c>
       <c r="N26">
-        <v>15.91764048839522</v>
+        <v>17.50635634543891</v>
       </c>
       <c r="O26">
         <v>1</v>
       </c>
       <c r="P26">
-        <v>88.6053446982134</v>
+        <v>71.85227137039857</v>
       </c>
       <c r="Q26">
-        <v>105.6460815578028</v>
+        <v>92.06894339997392</v>
       </c>
       <c r="R26">
-        <v>114.4357073062812</v>
+        <v>104.0337265406604</v>
       </c>
       <c r="S26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T26" t="b">
         <v>1</v>
@@ -2315,55 +2312,55 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
         <v>85</v>
       </c>
       <c r="G27">
-        <v>90.74209142719931</v>
+        <v>83.30807275110952</v>
       </c>
       <c r="H27">
-        <v>109.4557330066351</v>
+        <v>103.944024092142</v>
       </c>
       <c r="I27">
-        <v>119.9174856971819</v>
+        <v>112.2921420998412</v>
       </c>
       <c r="J27">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
       </c>
       <c r="L27">
-        <v>1.607789512414177</v>
+        <v>3.517681856451785</v>
       </c>
       <c r="M27">
-        <v>0.5980526218964557</v>
+        <v>0.5602897679435269</v>
       </c>
       <c r="N27">
-        <v>22.72292425632461</v>
+        <v>29.76731393537263</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>82.11655978878755</v>
+        <v>73.40239789956115</v>
       </c>
       <c r="Q27">
-        <v>100.8302013682233</v>
+        <v>94.03834924059366</v>
       </c>
       <c r="R27">
-        <v>111.2919540587701</v>
+        <v>102.3864672482928</v>
       </c>
       <c r="S27" t="s">
         <v>106</v>
@@ -2377,28 +2374,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
         <v>86</v>
       </c>
       <c r="G28">
-        <v>83.30807275110952</v>
+        <v>86.81419090441165</v>
       </c>
       <c r="H28">
-        <v>103.944024092142</v>
+        <v>105.5790260595306</v>
       </c>
       <c r="I28">
-        <v>112.2921420998412</v>
+        <v>114.9575278813161</v>
       </c>
       <c r="J28">
         <v>180</v>
@@ -2407,28 +2404,28 @@
         <v>1</v>
       </c>
       <c r="L28">
-        <v>3.517681856451785</v>
+        <v>1.8710546231918</v>
       </c>
       <c r="M28">
-        <v>0.5602897679435269</v>
+        <v>0.5842100837351556</v>
       </c>
       <c r="N28">
-        <v>29.76731393537263</v>
+        <v>17.34211485240496</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P28">
-        <v>73.40239789956115</v>
+        <v>78.0102504536203</v>
       </c>
       <c r="Q28">
-        <v>94.03834924059366</v>
+        <v>96.77508560873922</v>
       </c>
       <c r="R28">
-        <v>102.3864672482928</v>
+        <v>106.1535874305248</v>
       </c>
       <c r="S28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T28" t="b">
         <v>1</v>
@@ -2439,28 +2436,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s">
         <v>87</v>
       </c>
       <c r="G29">
-        <v>99.58053929638515</v>
+        <v>95.22398406058885</v>
       </c>
       <c r="H29">
-        <v>118.3453744515041</v>
+        <v>110.056660789208</v>
       </c>
       <c r="I29">
-        <v>127.7238762732897</v>
+        <v>115.4831152956049</v>
       </c>
       <c r="J29">
         <v>180</v>
@@ -2469,28 +2466,28 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>1.8710546231918</v>
+        <v>0.974739867166567</v>
       </c>
       <c r="M29">
-        <v>0.5842100837351556</v>
+        <v>0.7833911406296518</v>
       </c>
       <c r="N29">
-        <v>17.34211485240496</v>
+        <v>13.02652528635754</v>
       </c>
       <c r="O29">
         <v>2</v>
       </c>
       <c r="P29">
-        <v>90.79957716162518</v>
+        <v>85.31830920904048</v>
       </c>
       <c r="Q29">
-        <v>109.5644123167441</v>
+        <v>100.1509859376596</v>
       </c>
       <c r="R29">
-        <v>118.9429141385297</v>
+        <v>105.5774404440565</v>
       </c>
       <c r="S29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T29" t="b">
         <v>1</v>
@@ -2501,28 +2498,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
         <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>88</v>
       </c>
       <c r="G30">
-        <v>108.5423025821379</v>
+        <v>104.952101211129</v>
       </c>
       <c r="H30">
-        <v>123.3749793107571</v>
+        <v>119.3249947674968</v>
       </c>
       <c r="I30">
-        <v>128.801433817154</v>
+        <v>124.2604438794202</v>
       </c>
       <c r="J30">
         <v>180</v>
@@ -2531,28 +2528,28 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>0.974739867166567</v>
+        <v>0.8736555559417358</v>
       </c>
       <c r="M30">
-        <v>0.7833911406296518</v>
+        <v>0.7815861110145661</v>
       </c>
       <c r="N30">
-        <v>13.02652528635754</v>
+        <v>17.42084568180142</v>
       </c>
       <c r="O30">
         <v>2</v>
       </c>
       <c r="P30">
-        <v>102.9244183821658</v>
+        <v>104.952101211129</v>
       </c>
       <c r="Q30">
-        <v>117.757095110785</v>
+        <v>119.3249947674968</v>
       </c>
       <c r="R30">
-        <v>123.1835496171819</v>
+        <v>124.2604438794202</v>
       </c>
       <c r="S30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T30" t="b">
         <v>1</v>
@@ -2563,28 +2560,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
         <v>89</v>
       </c>
       <c r="G31">
-        <v>96.97227435582539</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="H31">
-        <v>111.3451679121932</v>
+        <v>109.0023288480263</v>
       </c>
       <c r="I31">
-        <v>116.2806170241165</v>
+        <v>122.1019161411614</v>
       </c>
       <c r="J31">
         <v>180</v>
@@ -2593,28 +2590,28 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>0.8736555559417358</v>
+        <v>4.478907793936024</v>
       </c>
       <c r="M31">
-        <v>0.7815861110145661</v>
+        <v>0.440136525757997</v>
       </c>
       <c r="N31">
-        <v>17.42084568180142</v>
+        <v>34.10618101429455</v>
       </c>
       <c r="O31">
         <v>2</v>
       </c>
       <c r="P31">
-        <v>88.36859904779647</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="Q31">
-        <v>102.7414926041643</v>
+        <v>109.0023288480263</v>
       </c>
       <c r="R31">
-        <v>107.6769417160876</v>
+        <v>122.1019161411614</v>
       </c>
       <c r="S31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T31" t="b">
         <v>1</v>
@@ -2625,28 +2622,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
         <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s">
         <v>90</v>
       </c>
       <c r="G32">
-        <v>118.0358497359536</v>
+        <v>105.4824461288021</v>
       </c>
       <c r="H32">
-        <v>139.4433870243834</v>
+        <v>125.9007676398808</v>
       </c>
       <c r="I32">
-        <v>151.5851465350355</v>
+        <v>137.9210891509594</v>
       </c>
       <c r="J32">
         <v>180</v>
@@ -2655,28 +2652,28 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>2.171939602406073</v>
+        <v>2.306810552860246</v>
       </c>
       <c r="M32">
-        <v>0.4570150993984818</v>
+        <v>0.4873754326977231</v>
       </c>
       <c r="N32">
-        <v>26.79734157293274</v>
+        <v>19.440198958216</v>
       </c>
       <c r="O32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32">
-        <v>109.4103180975419</v>
+        <v>97.0571796331528</v>
       </c>
       <c r="Q32">
-        <v>130.8178553859717</v>
+        <v>117.4755011442315</v>
       </c>
       <c r="R32">
-        <v>142.9596148966238</v>
+        <v>129.4958226553101</v>
       </c>
       <c r="S32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T32" t="b">
         <v>1</v>
@@ -2687,28 +2684,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
         <v>91</v>
       </c>
       <c r="G33">
-        <v>112.552971233474</v>
+        <v>113.9394013922088</v>
       </c>
       <c r="H33">
-        <v>132.9712927445526</v>
+        <v>135.908577946192</v>
       </c>
       <c r="I33">
-        <v>144.9916142556312</v>
+        <v>149.4895322779529</v>
       </c>
       <c r="J33">
         <v>180</v>
@@ -2717,28 +2714,28 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>2.306810552860246</v>
+        <v>2.494804901151978</v>
       </c>
       <c r="M33">
-        <v>0.4873754326977231</v>
+        <v>0.445598910855116</v>
       </c>
       <c r="N33">
-        <v>19.440198958216</v>
+        <v>20.34535693147248</v>
       </c>
       <c r="O33">
         <v>1</v>
       </c>
       <c r="P33">
-        <v>102.9931829663858</v>
+        <v>104.0337265406604</v>
       </c>
       <c r="Q33">
-        <v>123.4115044774644</v>
+        <v>126.0029030946436</v>
       </c>
       <c r="R33">
-        <v>135.4318259885431</v>
+        <v>139.5838574264045</v>
       </c>
       <c r="S33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T33" t="b">
         <v>1</v>
@@ -2749,28 +2746,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F34" t="s">
         <v>92</v>
       </c>
       <c r="G34">
-        <v>86.05407488822445</v>
+        <v>115.984035077443</v>
       </c>
       <c r="H34">
-        <v>107.0726497510757</v>
+        <v>130.5453171769986</v>
       </c>
       <c r="I34">
-        <v>119.1588912805937</v>
+        <v>136.8144881654431</v>
       </c>
       <c r="J34">
         <v>180</v>
@@ -2779,28 +2776,28 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>4.403269646749423</v>
+        <v>1.057798217128584</v>
       </c>
       <c r="M34">
-        <v>0.4495912941563222</v>
+        <v>0.7649337295269814</v>
       </c>
       <c r="N34">
-        <v>33.7647588221328</v>
+        <v>13.42643586024874</v>
       </c>
       <c r="O34">
         <v>1</v>
       </c>
       <c r="P34">
-        <v>86.05407488822445</v>
+        <v>107.1800946266517</v>
       </c>
       <c r="Q34">
-        <v>107.0726497510757</v>
+        <v>121.7413767262073</v>
       </c>
       <c r="R34">
-        <v>119.1588912805937</v>
+        <v>128.0105477146518</v>
       </c>
       <c r="S34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T34" t="b">
         <v>1</v>
@@ -2811,28 +2808,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
         <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F35" t="s">
         <v>93</v>
       </c>
       <c r="G35">
-        <v>124.4411423732947</v>
+        <v>106.4826699159122</v>
       </c>
       <c r="H35">
-        <v>139.0024244728503</v>
+        <v>123.1528953251573</v>
       </c>
       <c r="I35">
-        <v>145.2715954612948</v>
+        <v>131.5684540677358</v>
       </c>
       <c r="J35">
         <v>180</v>
@@ -2841,28 +2838,28 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>1.057798217128584</v>
+        <v>1.304041604369885</v>
       </c>
       <c r="M35">
-        <v>0.7649337295269814</v>
+        <v>0.6739895989075286</v>
       </c>
       <c r="N35">
-        <v>13.42643586024874</v>
+        <v>20.52918936489361</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35">
-        <v>118.8725284606768</v>
+        <v>106.4826699159122</v>
       </c>
       <c r="Q35">
-        <v>133.4338105602324</v>
+        <v>123.1528953251573</v>
       </c>
       <c r="R35">
-        <v>139.7029815486769</v>
+        <v>131.5684540677358</v>
       </c>
       <c r="S35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T35" t="b">
         <v>1</v>
@@ -2873,28 +2870,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36" t="s">
         <v>43</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F36" t="s">
         <v>94</v>
       </c>
       <c r="G36">
-        <v>121.7547777991096</v>
+        <v>125.5226730163729</v>
       </c>
       <c r="H36">
-        <v>139.7035136206564</v>
+        <v>145.0327011399565</v>
       </c>
       <c r="I36">
-        <v>148.9202494422031</v>
+        <v>156.2018403746513</v>
       </c>
       <c r="J36">
         <v>180</v>
@@ -2903,28 +2900,28 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>2.845453629675534</v>
+        <v>2.113150583946663</v>
       </c>
       <c r="M36">
-        <v>0.6443182962905583</v>
+        <v>0.4717123540133343</v>
       </c>
       <c r="N36">
-        <v>26.73295041172984</v>
+        <v>26.37275421739256</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36">
-        <v>111.8491029475612</v>
+        <v>125.5226730163729</v>
       </c>
       <c r="Q36">
-        <v>129.797838769108</v>
+        <v>145.0327011399565</v>
       </c>
       <c r="R36">
-        <v>139.0145745906547</v>
+        <v>156.2018403746513</v>
       </c>
       <c r="S36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T36" t="b">
         <v>1</v>
@@ -2935,28 +2932,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
         <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F37" t="s">
         <v>95</v>
       </c>
       <c r="G37">
-        <v>122.3232802406482</v>
+        <v>128.5096405819624</v>
       </c>
       <c r="H37">
-        <v>141.8333083642319</v>
+        <v>148.4489825617995</v>
       </c>
       <c r="I37">
-        <v>153.0024475989267</v>
+        <v>160.2736578749699</v>
       </c>
       <c r="J37">
         <v>180</v>
@@ -2965,28 +2962,28 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>2.113150583946663</v>
+        <v>2.064880504882156</v>
       </c>
       <c r="M37">
-        <v>0.4717123540133343</v>
+        <v>0.5411376655817433</v>
       </c>
       <c r="N37">
-        <v>26.37275421739256</v>
+        <v>18.27535057906223</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37">
-        <v>113.7196049326193</v>
+        <v>118.6039657304141</v>
       </c>
       <c r="Q37">
-        <v>133.229633056203</v>
+        <v>138.5433077102512</v>
       </c>
       <c r="R37">
-        <v>144.3987722908978</v>
+        <v>150.3679830234216</v>
       </c>
       <c r="S37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T37" t="b">
         <v>1</v>
@@ -2997,58 +2994,58 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F38" t="s">
         <v>96</v>
       </c>
       <c r="G38">
-        <v>121.9728032321447</v>
+        <v>136.8144881654431</v>
       </c>
       <c r="H38">
-        <v>141.4875062070714</v>
+        <v>159.2389881041379</v>
       </c>
       <c r="I38">
-        <v>152.480209181998</v>
+        <v>173.3977102650549</v>
       </c>
       <c r="J38">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
       </c>
       <c r="L38">
-        <v>3.686771208193226</v>
+        <v>2.412427120788479</v>
       </c>
       <c r="M38">
-        <v>0.5391535989758467</v>
+        <v>0.4639050842692268</v>
       </c>
       <c r="N38">
-        <v>30.53056448142775</v>
+        <v>19.94872317416675</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
       <c r="P38">
-        <v>121.9728032321447</v>
+        <v>128.0105477146518</v>
       </c>
       <c r="Q38">
-        <v>141.4875062070714</v>
+        <v>150.4350476533466</v>
       </c>
       <c r="R38">
-        <v>152.480209181998</v>
+        <v>164.5937698142636</v>
       </c>
       <c r="S38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T38" t="b">
         <v>1</v>
@@ -3062,25 +3059,25 @@
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
         <v>97</v>
       </c>
       <c r="G39">
-        <v>128.5010813119849</v>
+        <v>137.9210891509594</v>
       </c>
       <c r="H39">
-        <v>150.9255812506797</v>
+        <v>159.8902657049426</v>
       </c>
       <c r="I39">
-        <v>165.0843034115967</v>
+        <v>173.4712200367036</v>
       </c>
       <c r="J39">
         <v>240</v>
@@ -3089,28 +3086,28 @@
         <v>1</v>
       </c>
       <c r="L39">
-        <v>2.412427120788479</v>
+        <v>2.474777359477118</v>
       </c>
       <c r="M39">
-        <v>0.4639050842692268</v>
+        <v>0.4500494756717516</v>
       </c>
       <c r="N39">
-        <v>19.94872317416675</v>
+        <v>20.24892802711205</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39">
-        <v>118.9429141385297</v>
+        <v>129.4958226553101</v>
       </c>
       <c r="Q39">
-        <v>141.3674140772245</v>
+        <v>151.4649992092933</v>
       </c>
       <c r="R39">
-        <v>155.5261362381415</v>
+        <v>165.0459535410543</v>
       </c>
       <c r="S39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T39" t="b">
         <v>1</v>
@@ -3121,28 +3118,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E40" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F40" t="s">
         <v>98</v>
       </c>
       <c r="G40">
-        <v>148.9202494422031</v>
+        <v>131.833675800735</v>
       </c>
       <c r="H40">
-        <v>169.9388243050544</v>
+        <v>148.143708746864</v>
       </c>
       <c r="I40">
-        <v>182.0250658345724</v>
+        <v>156.0285194707708</v>
       </c>
       <c r="J40">
         <v>240</v>
@@ -3151,25 +3148,25 @@
         <v>1</v>
       </c>
       <c r="L40">
-        <v>4.375001305345046</v>
+        <v>1.42178203198294</v>
       </c>
       <c r="M40">
-        <v>0.4531248368318692</v>
+        <v>0.6445544920042652</v>
       </c>
       <c r="N40">
-        <v>33.63715866996027</v>
+        <v>21.37953689765456</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40">
-        <v>139.0145745906547</v>
+        <v>131.833675800735</v>
       </c>
       <c r="Q40">
-        <v>160.033149453506</v>
+        <v>148.143708746864</v>
       </c>
       <c r="R40">
-        <v>172.119390983024</v>
+        <v>156.0285194707708</v>
       </c>
       <c r="S40" t="s">
         <v>106</v>
@@ -3183,28 +3180,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F41" t="s">
         <v>99</v>
       </c>
       <c r="G41">
-        <v>135.9024674104284</v>
+        <v>121.7547777991096</v>
       </c>
       <c r="H41">
-        <v>153.6852816920291</v>
+        <v>142.2975441367244</v>
       </c>
       <c r="I41">
-        <v>163.0428737514077</v>
+        <v>153.9789771410058</v>
       </c>
       <c r="J41">
         <v>240</v>
@@ -3213,28 +3210,28 @@
         <v>1</v>
       </c>
       <c r="L41">
-        <v>1.711944804864733</v>
+        <v>4.438133580673728</v>
       </c>
       <c r="M41">
-        <v>0.6195678211411705</v>
+        <v>0.445233302415784</v>
       </c>
       <c r="N41">
-        <v>16.57603054194131</v>
+        <v>33.92213074609668</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41">
-        <v>130.3533477946764</v>
+        <v>111.8491029475612</v>
       </c>
       <c r="Q41">
-        <v>148.1361620762771</v>
+        <v>132.391869285176</v>
       </c>
       <c r="R41">
-        <v>157.4937541356557</v>
+        <v>144.0733022894574</v>
       </c>
       <c r="S41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T41" t="b">
         <v>1</v>
@@ -3245,7 +3242,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
         <v>30</v>
@@ -3254,19 +3251,19 @@
         <v>44</v>
       </c>
       <c r="E42" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F42" t="s">
         <v>100</v>
       </c>
       <c r="G42">
-        <v>151.5851465350355</v>
+        <v>150.2409240256919</v>
       </c>
       <c r="H42">
-        <v>171.0951746586192</v>
+        <v>168.0057591808108</v>
       </c>
       <c r="I42">
-        <v>182.2643138933139</v>
+        <v>177.3842610025962</v>
       </c>
       <c r="J42">
         <v>240</v>
@@ -3275,28 +3272,28 @@
         <v>1</v>
       </c>
       <c r="L42">
-        <v>2.080451140464154</v>
+        <v>1.797687027182534</v>
       </c>
       <c r="M42">
-        <v>0.4798872148839615</v>
+        <v>0.6005139939594369</v>
       </c>
       <c r="N42">
-        <v>26.13659157001889</v>
+        <v>16.9888634642122</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42">
-        <v>142.9596148966238</v>
+        <v>141.4369835749006</v>
       </c>
       <c r="Q42">
-        <v>162.4696430202075</v>
+        <v>159.2018187300195</v>
       </c>
       <c r="R42">
-        <v>173.6387822549022</v>
+        <v>168.580320551805</v>
       </c>
       <c r="S42" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T42" t="b">
         <v>1</v>
@@ -3307,28 +3304,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D43" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43">
-        <v>144.9916142556312</v>
+        <v>160.2736578749699</v>
       </c>
       <c r="H43">
-        <v>162.7564494107502</v>
+        <v>174.1063346035891</v>
       </c>
       <c r="I43">
-        <v>172.1349512325357</v>
+        <v>179.532789109986</v>
       </c>
       <c r="J43">
         <v>240</v>
@@ -3337,28 +3334,28 @@
         <v>1</v>
       </c>
       <c r="L43">
-        <v>1.797687027182534</v>
+        <v>0.9386225872442431</v>
       </c>
       <c r="M43">
-        <v>0.6005139939594369</v>
+        <v>0.7914172028346127</v>
       </c>
       <c r="N43">
-        <v>16.9888634642122</v>
+        <v>12.85262727191672</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43">
-        <v>136.2100749035394</v>
+        <v>150.3679830234216</v>
       </c>
       <c r="Q43">
-        <v>153.9749100586583</v>
+        <v>164.2006597520408</v>
       </c>
       <c r="R43">
-        <v>163.3534118804439</v>
+        <v>169.6271142584377</v>
       </c>
       <c r="S43" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T43" t="b">
         <v>1</v>
@@ -3375,22 +3372,22 @@
         <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E44" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F44" t="s">
         <v>102</v>
       </c>
       <c r="G44">
-        <v>152.9236501027265</v>
+        <v>122.1019161411614</v>
       </c>
       <c r="H44">
-        <v>166.8837186611424</v>
+        <v>141.616619116088</v>
       </c>
       <c r="I44">
-        <v>171.884453886225</v>
+        <v>152.6093220910147</v>
       </c>
       <c r="J44">
         <v>240</v>
@@ -3399,28 +3396,28 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>1.681614284379605</v>
+        <v>3.616951951699551</v>
       </c>
       <c r="M44">
-        <v>0.7897982144525494</v>
+        <v>0.5478810060375561</v>
       </c>
       <c r="N44">
-        <v>21.47950892254682</v>
+        <v>30.21540811531047</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44">
-        <v>152.9236501027265</v>
+        <v>122.1019161411614</v>
       </c>
       <c r="Q44">
-        <v>166.8837186611424</v>
+        <v>141.616619116088</v>
       </c>
       <c r="R44">
-        <v>171.884453886225</v>
+        <v>152.6093220910147</v>
       </c>
       <c r="S44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T44" t="b">
         <v>1</v>
@@ -3431,122 +3428,60 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F45" t="s">
         <v>103</v>
       </c>
       <c r="G45">
-        <v>153.0024475989267</v>
+        <v>152.6093220910147</v>
       </c>
       <c r="H45">
-        <v>171.2698157913762</v>
+        <v>169.9452734320472</v>
       </c>
       <c r="I45">
-        <v>181.4225173171591</v>
+        <v>178.2933914397464</v>
       </c>
       <c r="J45">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
       </c>
       <c r="L45">
-        <v>1.684852321935074</v>
+        <v>3.005558200720436</v>
       </c>
       <c r="M45">
-        <v>0.5787869195162316</v>
+        <v>0.6243052249099456</v>
       </c>
       <c r="N45">
-        <v>23.2794889917533</v>
+        <v>27.45564465602974</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45">
-        <v>144.3987722908978</v>
+        <v>144.0733022894574</v>
       </c>
       <c r="Q45">
-        <v>162.6661404833473</v>
+        <v>161.4092536304899</v>
       </c>
       <c r="R45">
-        <v>172.8188420091302</v>
+        <v>169.7573716381891</v>
       </c>
       <c r="S45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>27</v>
-      </c>
-      <c r="C46" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" t="s">
-        <v>38</v>
-      </c>
-      <c r="E46" t="s">
-        <v>57</v>
-      </c>
-      <c r="F46" t="s">
-        <v>104</v>
-      </c>
-      <c r="G46">
-        <v>145.2715954612948</v>
-      </c>
-      <c r="H46">
-        <v>163.0544097428956</v>
-      </c>
-      <c r="I46">
-        <v>172.4120018022741</v>
-      </c>
-      <c r="J46">
-        <v>300</v>
-      </c>
-      <c r="K46" t="b">
-        <v>1</v>
-      </c>
-      <c r="L46">
-        <v>1.698235657333516</v>
-      </c>
-      <c r="M46">
-        <v>0.6226142983703299</v>
-      </c>
-      <c r="N46">
-        <v>16.51002353530952</v>
-      </c>
-      <c r="O46">
-        <v>1</v>
-      </c>
-      <c r="P46">
-        <v>139.7029815486769</v>
-      </c>
-      <c r="Q46">
-        <v>157.4857958302777</v>
-      </c>
-      <c r="R46">
-        <v>166.8433878896562</v>
-      </c>
-      <c r="S46" t="s">
-        <v>107</v>
-      </c>
-      <c r="T46" t="b">
         <v>1</v>
       </c>
     </row>
